--- a/data/externalStats/File1/RPT_RPT3325127211997VZ_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT3325127211997VZ_externalStats.xlsx
@@ -2054,19 +2054,19 @@
       </c>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="39" t="n">
-        <v>115791</v>
+        <v>115790</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>2971148.640196562</v>
+        <v>2971146.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2832362</v>
+        <v>2832334</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>25.65958183448249</v>
+        <v>25.65978616630591</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.46098574155159</v>
+        <v>24.46095517747647</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -2134,13 +2134,13 @@
         <v>23842</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>1864813.399864435</v>
+        <v>1864963.399864435</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>2121209</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>78.21547688383673</v>
+        <v>78.22176830234189</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>88.96942370606493</v>
@@ -2208,19 +2208,19 @@
       </c>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="60" t="n">
-        <v>7921</v>
+        <v>7763</v>
       </c>
       <c r="E27" s="61" t="n">
-        <v>516620.4499400854</v>
+        <v>515166.4499400854</v>
       </c>
       <c r="F27" s="61" t="n">
-        <v>580697</v>
+        <v>568037</v>
       </c>
       <c r="G27" s="62" t="n">
-        <v>65.22161973741768</v>
+        <v>66.36177379107116</v>
       </c>
       <c r="H27" s="63" t="n">
-        <v>73.31107183436434</v>
+        <v>73.17235604791962</v>
       </c>
       <c r="I27" s="31" t="n"/>
       <c r="J27" s="31" t="n"/>
@@ -2285,19 +2285,19 @@
       </c>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="65" t="n">
-        <v>147554</v>
+        <v>147395</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>5352582.490001082</v>
+        <v>5351276.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5534268</v>
+        <v>5521580</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>36.27541435678519</v>
+        <v>36.30568533533079</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.50672973962075</v>
+        <v>37.46110790732386</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -2439,19 +2439,19 @@
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="70" t="n">
-        <v>154536</v>
+        <v>154377</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>5509965.570032656</v>
+        <v>5508659.570032656</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5879288</v>
+        <v>5866600</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>35.65489963524782</v>
+        <v>35.68316245316761</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.04477921002226</v>
+        <v>38.00177487579109</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -2650,19 +2650,19 @@
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="39" t="n">
-        <v>1068917</v>
+        <v>1068918</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>47347727.77691305</v>
+        <v>47347729.77691305</v>
       </c>
       <c r="F33" s="40" t="n">
-        <v>25837092</v>
+        <v>25837120</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>44.29504608581681</v>
+        <v>44.29500651772451</v>
       </c>
       <c r="H33" s="42" t="n">
-        <v>24.17127990292979</v>
+        <v>24.17128348479491</v>
       </c>
       <c r="I33" s="31" t="n"/>
       <c r="J33" s="31" t="n"/>
@@ -2804,19 +2804,19 @@
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="60" t="n">
-        <v>55117</v>
+        <v>55265</v>
       </c>
       <c r="E35" s="61" t="n">
-        <v>5536753.690037966</v>
+        <v>5537597.690037966</v>
       </c>
       <c r="F35" s="61" t="n">
-        <v>4379318</v>
+        <v>4391134</v>
       </c>
       <c r="G35" s="62" t="n">
-        <v>100.4545546752901</v>
+        <v>100.2008086499225</v>
       </c>
       <c r="H35" s="63" t="n">
-        <v>79.4549413066749</v>
+        <v>79.4559667058717</v>
       </c>
       <c r="I35" s="31" t="n"/>
       <c r="J35" s="31" t="n"/>
@@ -2881,19 +2881,19 @@
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="65" t="n">
-        <v>1371213</v>
+        <v>1371362</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>79307125.54702628</v>
+        <v>79307971.54702628</v>
       </c>
       <c r="F36" s="66" t="n">
-        <v>52386298</v>
+        <v>52398142</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>57.83720366349085</v>
+        <v>57.83153649220722</v>
       </c>
       <c r="H36" s="68" t="n">
-        <v>38.20434753754522</v>
+        <v>38.2088332621146</v>
       </c>
       <c r="I36" s="31" t="n"/>
       <c r="J36" s="31" t="n"/>
@@ -3035,19 +3035,19 @@
       </c>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="70" t="n">
-        <v>1372025</v>
+        <v>1372174</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>79351676.9670254</v>
+        <v>79352522.9670254</v>
       </c>
       <c r="F38" s="71" t="n">
-        <v>52413843</v>
+        <v>52425687</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>57.83544539423509</v>
+        <v>57.82978176749115</v>
       </c>
       <c r="H38" s="73" t="n">
-        <v>38.20181337803611</v>
+        <v>38.20629672330185</v>
       </c>
       <c r="I38" s="31" t="n"/>
       <c r="J38" s="31" t="n"/>
@@ -3292,7 +3292,7 @@
         <v>1571920.225377287</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>3118.807607</v>
+        <v>3118.807606999999</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -3322,13 +3322,13 @@
         <v>271021</v>
       </c>
       <c r="E42" s="51" t="n">
-        <v>28287457.4799397</v>
+        <v>28287607.4799397</v>
       </c>
       <c r="F42" s="51" t="n">
         <v>24291097</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>104.3736739217245</v>
+        <v>104.3742273843713</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>89.62809892960324</v>
@@ -3396,19 +3396,19 @@
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="60" t="n">
-        <v>63038</v>
+        <v>63028</v>
       </c>
       <c r="E43" s="61" t="n">
-        <v>6053374.139978051</v>
+        <v>6052764.139978051</v>
       </c>
       <c r="F43" s="61" t="n">
-        <v>4960015</v>
+        <v>4959171</v>
       </c>
       <c r="G43" s="62" t="n">
-        <v>96.02738253082349</v>
+        <v>96.03293996284272</v>
       </c>
       <c r="H43" s="63" t="n">
-        <v>78.68293727592881</v>
+        <v>78.68203020879609</v>
       </c>
       <c r="I43" s="31" t="n"/>
       <c r="J43" s="31" t="n"/>
@@ -3473,19 +3473,19 @@
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="65" t="n">
-        <v>1518767</v>
+        <v>1518757</v>
       </c>
       <c r="E44" s="66" t="n">
-        <v>84659708.03702736</v>
+        <v>84659248.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57920566</v>
+        <v>57919722</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>55.74239368976766</v>
+        <v>55.74245783692017</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13657131080673</v>
+        <v>38.13626669704239</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -3592,19 +3592,19 @@
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="70" t="n">
-        <v>1526561</v>
+        <v>1526551</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>84861642.53705806</v>
+        <v>84861182.53705806</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58293131</v>
+        <v>58292287</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>55.59007634615194</v>
+        <v>55.59013916800556</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18591657981568</v>
+        <v>38.18561384454237</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>42381311.56098315</v>
+        <v>42381311.56098316</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>56332.87391490716</v>
+        <v>55967.28423690716</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>7301290.376945708</v>
+        <v>7301290.376945707</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>3658.06139595</v>
@@ -4313,7 +4313,7 @@
         <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>1115.559154852212</v>
+        <v>1115.559154852213</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>271.7232861003955</v>
@@ -4328,10 +4328,10 @@
         <v>3618.385647774603</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1143.041250161384</v>
+        <v>1143.041250161383</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -4346,13 +4346,13 @@
         <v>1157.115197318205</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>271.4243920631148</v>
+        <v>271.4243920631149</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5068.100277253077</v>
+        <v>5068.100277253076</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -4397,13 +4397,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.965722454756</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3980.972262557945</v>
+        <v>3980.970361894082</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -4415,10 +4415,10 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.014497408322</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4383.105585846696</v>
+        <v>4383.100197657335</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -4427,13 +4427,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>449.3890492690071</v>
+        <v>449.3890492690072</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.04785981867</v>
+        <v>4398.986749732734</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087677</v>
+        <v>4848.375799001741</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -4447,7 +4447,7 @@
         <v>1007293.24253283</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>4489.79398771465</v>
+        <v>4489.793987714651</v>
       </c>
     </row>
     <row r="60">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>989013.9075189303</v>
+        <v>989013.9075189302</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2740.1603206045</v>
@@ -4556,46 +4556,46 @@
         <v>2760.937391194303</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.4849430367736</v>
+        <v>710.4849430367738</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>245.7140354696757</v>
+        <v>245.7140354696758</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>406.9924088095189</v>
+        <v>406.9921954129193</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>4124.128778510271</v>
+        <v>4124.128565113671</v>
       </c>
       <c r="P61" s="130" t="n">
         <v>2896.738881877362</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>758.54766362367</v>
+        <v>758.5476636236698</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>256.0029063005556</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>412.9240454842196</v>
+        <v>412.9234870249217</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4324.213497285807</v>
+        <v>4324.212938826509</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3030.200510783198</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.719726109169</v>
+        <v>802.7197261091691</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7806947937877</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4526.852231508797</v>
+        <v>4526.846288841426</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>860148.7703082537</v>
+        <v>859518.8636664032</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>2703.960876253711</v>
+        <v>2695.022586253711</v>
       </c>
     </row>
     <row r="62">
@@ -4709,55 +4709,55 @@
         <v>229</v>
       </c>
       <c r="G63" s="131" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H63" s="132" t="n">
-        <v>5063</v>
+        <v>5073</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6063.963028375118</v>
+        <v>6063.95385411218</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076215</v>
+        <v>1028.516213076213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>482.4032427834436</v>
+        <v>477.505793182102</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481004</v>
+        <v>2653.723479434723</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10219.64392971578</v>
+        <v>10223.69933980522</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>6897.230573753623</v>
+        <v>6897.219061859658</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1192.650797495556</v>
+        <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.4264574542294</v>
+        <v>513.29853309591</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>2834.005975254689</v>
+        <v>2842.574994921451</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11443.3138039581</v>
+        <v>11445.74338737257</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971947</v>
+        <v>7858.807911385724</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473848</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611685</v>
+        <v>537.0837375110368</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886602</v>
+        <v>3103.122540499337</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12892.15756086994</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="134" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H64" s="135" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="J64" s="133" t="n">
         <v>0</v>
@@ -4805,10 +4805,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -5048,16 +5048,16 @@
         <v>36007.66823156678</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624416</v>
+        <v>5431.185034624418</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>1362.310849873848</v>
+        <v>1362.310135579192</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>44445.04077414373</v>
+        <v>44445.04005984907</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>34052.38752490297</v>
@@ -5066,28 +5066,28 @@
         <v>4646.024039270555</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1463.882211566669</v>
+        <v>1463.88221156667</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>1412.269704923372</v>
+        <v>1412.267794898619</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066356</v>
+        <v>41574.56157063881</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360797</v>
+        <v>33426.99961360798</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183502</v>
+        <v>4250.604456183503</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1620.213936787498</v>
+        <v>1620.19142932314</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355702</v>
+        <v>40672.84056609267</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>355269.4191011894</v>
+        <v>355269.4191011893</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>752.6685311072612</v>
@@ -5120,55 +5120,55 @@
         <v>3358</v>
       </c>
       <c r="G68" s="143" t="n">
-        <v>6165</v>
+        <v>6175</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>48448</v>
+        <v>48468</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>48409.5719511969</v>
+        <v>48409.56277693396</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>8285.745345589618</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2999.721861871521</v>
+        <v>2994.82441227018</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.03232728299</v>
+        <v>8047.991532881591</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69996.87349981788</v>
+        <v>70009.88811550592</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>47464.74262830856</v>
+        <v>47464.73111641459</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>7740.263750551166</v>
+        <v>7740.263750551165</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2910.660891075922</v>
+        <v>2904.532966717603</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8651.780774253313</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418758</v>
+        <v>69176.53470059541</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>47955.58247823487</v>
+        <v>47955.56872364866</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>7603.582751084724</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326608</v>
+        <v>2899.087602976476</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953928</v>
+        <v>9550.081414348999</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457616</v>
+        <v>70633.91844764759</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5674,7 +5674,7 @@
         <v>128.2800174617996</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>42.93598052467679</v>
+        <v>42.9359805246768</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>12.1098980688175</v>
@@ -5689,7 +5689,7 @@
         <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13363173601854</v>
+        <v>44.13363173601853</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44747003933478</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -5747,10 +5747,10 @@
         <v>46.76876318724293</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>293.459219768103</v>
+        <v>293.454975391339</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>340.2279829553459</v>
+        <v>340.2237385785819</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -5762,10 +5762,10 @@
         <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>346.9012428180422</v>
+        <v>346.8954687025169</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>397.9406897215059</v>
+        <v>397.9349156059806</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -5774,13 +5774,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446341</v>
+        <v>55.9139763744634</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>429.6897602068635</v>
+        <v>429.6820421563438</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>485.6037365813269</v>
+        <v>485.5960185308072</v>
       </c>
     </row>
     <row r="78">
@@ -5881,10 +5881,10 @@
         <v>51.20888766333687</v>
       </c>
       <c r="M79" s="131" t="n">
-        <v>6.696987462960856</v>
+        <v>6.696890602695233</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2866.74538671823</v>
+        <v>2866.745289857964</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2967.764433241743</v>
@@ -5896,25 +5896,25 @@
         <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869917</v>
+        <v>7.015452520844691</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907147</v>
+        <v>3178.988967134122</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181512</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>170.896069546928</v>
+        <v>170.8960695469279</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.0050868260645</v>
+        <v>73.00508682606451</v>
       </c>
       <c r="Y79" s="131" t="n">
-        <v>7.392892254635247</v>
+        <v>7.392759464140354</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3496.28003080914</v>
+        <v>3496.279898018644</v>
       </c>
     </row>
     <row r="80">
@@ -6015,10 +6015,10 @@
         <v>197.3705810333049</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>176.0290901661888</v>
+        <v>176.0265442118289</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1576.803216563795</v>
+        <v>1576.800670609435</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>1090.701571439859</v>
@@ -6030,10 +6030,10 @@
         <v>218.5733671538328</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>262.6291555824171</v>
+        <v>262.6247841622621</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1743.814959403218</v>
+        <v>1743.810587983063</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>1148.288930966286</v>
@@ -6045,10 +6045,10 @@
         <v>257.0678553579128</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>346.9079872526063</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1930.5145187721</v>
+        <v>1930.508287640667</v>
       </c>
     </row>
     <row r="82">
@@ -6082,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -6097,10 +6097,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -6112,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
     </row>
     <row r="83">
@@ -6284,13 +6284,13 @@
         <v>251057.4170218568</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557481</v>
+        <v>57266.91038557482</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>969.9340240824498</v>
+        <v>969.9199956752398</v>
       </c>
       <c r="N85" s="141" t="n">
-        <v>1413346.604401443</v>
+        <v>1413346.590373036</v>
       </c>
       <c r="P85" s="139" t="n">
         <v>1115952.652029663</v>
@@ -6302,10 +6302,10 @@
         <v>57819.37211079447</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.62527354356</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427459.890486034</v>
+        <v>1427459.872249224</v>
       </c>
       <c r="V85" s="139" t="n">
         <v>1125695.480763512</v>
@@ -6317,10 +6317,10 @@
         <v>58283.77647998057</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>1183.845442488683</v>
+        <v>1183.824178358655</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1438770.993451629</v>
+        <v>1438770.972187499</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -6354,10 +6354,10 @@
         <v>57574.36851552752</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>1446.119321479702</v>
+        <v>1446.098405881103</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>1418489.735973902</v>
+        <v>1418489.712512349</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>1120142.848455235</v>
@@ -6369,10 +6369,10 @@
         <v>58164.31294237659</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048319</v>
+        <v>1712.160978929183</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1433231.575897314</v>
+        <v>1433231.543026775</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>1130223.153690994</v>
@@ -6384,10 +6384,10 @@
         <v>58682.4705383649</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>1967.836082202788</v>
+        <v>1967.800736100312</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>1445222.459991917</v>
+        <v>1445222.418414683</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6897,7 +6897,7 @@
         <v>1187.174881897402</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -6909,16 +6909,16 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029856</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>284.1315318890079</v>
+        <v>284.131531889008</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125526</v>
       </c>
     </row>
     <row r="95">
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>3918.426842886722</v>
+        <v>3918.420697846095</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4321.200245513292</v>
+        <v>4321.194100472664</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.909966110838</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.035113263316</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -6979,13 +6979,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>505.3030256434705</v>
+        <v>505.3030256434706</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025534</v>
+        <v>4828.668791889078</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669004</v>
+        <v>5333.971817532548</v>
       </c>
     </row>
     <row r="96">
@@ -7077,49 +7077,49 @@
         <v>35788</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5457.960764601422</v>
+        <v>5457.960764601421</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>822.3010812215867</v>
+        <v>822.3010812215869</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>296.9229231330126</v>
+        <v>296.9229231330127</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>413.6893962724798</v>
+        <v>413.6890860156146</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>6990.874165228502</v>
+        <v>6990.873854971635</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119106</v>
+        <v>5864.503315119105</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>899.8761975097219</v>
+        <v>899.8761975097217</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>318.8834537860382</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>419.9396147780895</v>
+        <v>419.9389395457664</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192956</v>
+        <v>7503.201905960631</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6275.186492964711</v>
+        <v>6275.18649296471</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560969</v>
+        <v>973.615795656097</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>435.1795297157934</v>
+        <v>435.173454257928</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8023.132262317936</v>
+        <v>8023.12618686007</v>
       </c>
     </row>
     <row r="98">
@@ -7205,55 +7205,55 @@
         <v>292</v>
       </c>
       <c r="G99" s="131" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H99" s="132" t="n">
-        <v>5915</v>
+        <v>5925</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7101.643792012008</v>
+        <v>7101.634617748903</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>674.8763742154042</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647193</v>
+        <v>2829.750023646551</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11800.50001041466</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>7987.932145193219</v>
+        <v>7987.920633299276</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1364.561662722641</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>737.999824608065</v>
+        <v>731.8719002497455</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837106</v>
+        <v>3105.199779083713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>13187.12876336103</v>
+        <v>13189.55397535537</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>9007.110596938059</v>
+        <v>9007.096842351835</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1571.393116669147</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>801.4714782190786</v>
+        <v>794.1515928689478</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139209</v>
+        <v>3450.02429662051</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14821.73831296549</v>
+        <v>14822.66584851044</v>
       </c>
     </row>
     <row r="100">
@@ -7272,10 +7272,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="134" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H100" s="135" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="J100" s="133" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7317,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
     </row>
     <row r="101">
@@ -7489,13 +7489,13 @@
         <v>256488.6020564813</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365349</v>
+        <v>58910.7870436535</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>2332.244873956298</v>
+        <v>2332.230131254431</v>
       </c>
       <c r="N103" s="141" t="n">
-        <v>1457791.645175586</v>
+        <v>1457791.630432884</v>
       </c>
       <c r="P103" s="139" t="n">
         <v>1150005.039554566</v>
@@ -7507,10 +7507,10 @@
         <v>59283.25432236114</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.893068442178</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469034.453966697</v>
+        <v>1469034.433819862</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>1159122.48037712</v>
@@ -7522,10 +7522,10 @@
         <v>59658.82154695861</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>2804.059379276181</v>
+        <v>2804.015607681795</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>1479443.856525186</v>
+        <v>1479443.812753592</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7544,55 +7544,55 @@
         <v>3504</v>
       </c>
       <c r="G104" s="143" t="n">
-        <v>7086</v>
+        <v>7096</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>52114</v>
+        <v>52134</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1156324.899075631</v>
+        <v>1156324.889901368</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>259663.6372678835</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739904</v>
+        <v>60569.1929277977</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762692</v>
+        <v>9494.089938762692</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1488486.609473719</v>
+        <v>1488499.600627854</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1167607.591083543</v>
+        <v>1167607.579571649</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>260689.8596166228</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>61074.97383345251</v>
+        <v>61068.84590909419</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>10355.40908930828</v>
+        <v>10363.9417531825</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1502397.119851501</v>
+        <v>1502408.07772737</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1178178.736169229</v>
+        <v>1178178.722414643</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>261605.6744441866</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61588.87802669151</v>
+        <v>61581.55814134137</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>11509.73965015672</v>
+        <v>11517.88215044931</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1515847.266826493</v>
+        <v>1515856.33686233</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>1578675</v>
+        <v>1578685</v>
       </c>
     </row>
     <row r="109"/>
@@ -8578,19 +8578,19 @@
       </c>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="39" t="n">
-        <v>115791</v>
+        <v>115790</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>2971148.640196562</v>
+        <v>2971146.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2832362</v>
+        <v>2832334</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>25.65958183448249</v>
+        <v>25.65978616630591</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.46098574155159</v>
+        <v>24.46095517747647</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -8658,13 +8658,13 @@
         <v>23842</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>1864813.399864435</v>
+        <v>1864963.399864435</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>2121209</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>78.21547688383673</v>
+        <v>78.22176830234189</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>88.96942370606493</v>
@@ -8732,19 +8732,19 @@
       </c>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="60" t="n">
-        <v>7921</v>
+        <v>7763</v>
       </c>
       <c r="E27" s="61" t="n">
-        <v>516620.4499400854</v>
+        <v>515166.4499400854</v>
       </c>
       <c r="F27" s="61" t="n">
-        <v>580697</v>
+        <v>568037</v>
       </c>
       <c r="G27" s="62" t="n">
-        <v>65.22161973741768</v>
+        <v>66.36177379107116</v>
       </c>
       <c r="H27" s="63" t="n">
-        <v>73.31107183436434</v>
+        <v>73.17235604791962</v>
       </c>
       <c r="I27" s="31" t="n"/>
       <c r="J27" s="31" t="n"/>
@@ -8809,19 +8809,19 @@
       </c>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="65" t="n">
-        <v>147554</v>
+        <v>147395</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>5352582.490001082</v>
+        <v>5351276.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5534268</v>
+        <v>5521580</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>36.27541435678519</v>
+        <v>36.30568533533079</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.50672973962075</v>
+        <v>37.46110790732386</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>337.2342832499999</v>
+        <v>337.23428325</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -8963,19 +8963,19 @@
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="70" t="n">
-        <v>154536</v>
+        <v>154377</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>5509965.570032656</v>
+        <v>5508659.570032656</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5879288</v>
+        <v>5866600</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>35.65489963524782</v>
+        <v>35.68316245316761</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.04477921002226</v>
+        <v>38.00177487579109</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -9174,19 +9174,19 @@
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="39" t="n">
-        <v>1068917</v>
+        <v>1068918</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>47347727.77691305</v>
+        <v>47347729.77691305</v>
       </c>
       <c r="F33" s="40" t="n">
-        <v>25837092</v>
+        <v>25837120</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>44.29504608581681</v>
+        <v>44.29500651772451</v>
       </c>
       <c r="H33" s="42" t="n">
-        <v>24.17127990292979</v>
+        <v>24.17128348479491</v>
       </c>
       <c r="I33" s="31" t="n"/>
       <c r="J33" s="31" t="n"/>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5329025.207125469</v>
+        <v>5358616.267363989</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>765.0549989487085</v>
+        <v>765.0549989487084</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -9328,19 +9328,19 @@
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="60" t="n">
-        <v>55117</v>
+        <v>55265</v>
       </c>
       <c r="E35" s="61" t="n">
-        <v>5536753.690037966</v>
+        <v>5537597.690037966</v>
       </c>
       <c r="F35" s="61" t="n">
-        <v>4379318</v>
+        <v>4391134</v>
       </c>
       <c r="G35" s="62" t="n">
-        <v>100.4545546752901</v>
+        <v>100.2008086499225</v>
       </c>
       <c r="H35" s="63" t="n">
-        <v>79.4549413066749</v>
+        <v>79.4559667058717</v>
       </c>
       <c r="I35" s="31" t="n"/>
       <c r="J35" s="31" t="n"/>
@@ -9405,19 +9405,19 @@
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="65" t="n">
-        <v>1371213</v>
+        <v>1371362</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>79307125.54702628</v>
+        <v>79307971.54702628</v>
       </c>
       <c r="F36" s="66" t="n">
-        <v>52386298</v>
+        <v>52398142</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>57.83720366349085</v>
+        <v>57.83153649220722</v>
       </c>
       <c r="H36" s="68" t="n">
-        <v>38.20434753754522</v>
+        <v>38.2088332621146</v>
       </c>
       <c r="I36" s="31" t="n"/>
       <c r="J36" s="31" t="n"/>
@@ -9559,19 +9559,19 @@
       </c>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="70" t="n">
-        <v>1372025</v>
+        <v>1372174</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>79351676.9670254</v>
+        <v>79352522.9670254</v>
       </c>
       <c r="F38" s="71" t="n">
-        <v>52413843</v>
+        <v>52425687</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>57.83544539423509</v>
+        <v>57.82978176749115</v>
       </c>
       <c r="H38" s="73" t="n">
-        <v>38.20181337803611</v>
+        <v>38.20629672330185</v>
       </c>
       <c r="I38" s="31" t="n"/>
       <c r="J38" s="31" t="n"/>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="AN38" s="58" t="n">
-        <v>5364.132132343527</v>
+        <v>5364.132132343528</v>
       </c>
     </row>
     <row r="39">
@@ -9672,7 +9672,7 @@
         <v>1812297.191199682</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>5750.8412192</v>
+        <v>5750.841219200001</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -9846,13 +9846,13 @@
         <v>271021</v>
       </c>
       <c r="E42" s="51" t="n">
-        <v>28287457.4799397</v>
+        <v>28287607.4799397</v>
       </c>
       <c r="F42" s="51" t="n">
         <v>24291097</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>104.3736739217245</v>
+        <v>104.3742273843713</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>89.62809892960324</v>
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1696818.117976401</v>
+        <v>1696818.1179764</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>3262.52226153056</v>
+        <v>3262.522261530561</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9920,19 +9920,19 @@
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="60" t="n">
-        <v>63038</v>
+        <v>63028</v>
       </c>
       <c r="E43" s="61" t="n">
-        <v>6053374.139978051</v>
+        <v>6052764.139978051</v>
       </c>
       <c r="F43" s="61" t="n">
-        <v>4960015</v>
+        <v>4959171</v>
       </c>
       <c r="G43" s="62" t="n">
-        <v>96.02738253082349</v>
+        <v>96.03293996284272</v>
       </c>
       <c r="H43" s="63" t="n">
-        <v>78.68293727592881</v>
+        <v>78.68203020879609</v>
       </c>
       <c r="I43" s="31" t="n"/>
       <c r="J43" s="31" t="n"/>
@@ -9997,19 +9997,19 @@
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="65" t="n">
-        <v>1518767</v>
+        <v>1518757</v>
       </c>
       <c r="E44" s="66" t="n">
-        <v>84659708.03702736</v>
+        <v>84659248.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57920566</v>
+        <v>57919722</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>55.74239368976766</v>
+        <v>55.74245783692017</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13657131080673</v>
+        <v>38.13626669704239</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -10047,7 +10047,7 @@
         <v>1483373.414491142</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>2395.247496611513</v>
+        <v>2395.247496611512</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -10116,19 +10116,19 @@
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="70" t="n">
-        <v>1526561</v>
+        <v>1526551</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>84861642.53705806</v>
+        <v>84861182.53705806</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58293131</v>
+        <v>58292287</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>55.59007634615194</v>
+        <v>55.59013916800556</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18591657981568</v>
+        <v>38.18561384454237</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>57429759.98745834</v>
+        <v>57459351.04769687</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>6112.663549744621</v>
@@ -10237,7 +10237,7 @@
         <v>50483914.26914035</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>65432.22259011088</v>
+        <v>64971.57959583089</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -10404,7 +10404,7 @@
         <v>9220815.753906675</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>4451.741441899038</v>
+        <v>4451.741441899039</v>
       </c>
     </row>
     <row r="53">
@@ -10837,7 +10837,7 @@
         <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>1115.559154852212</v>
+        <v>1115.559154852213</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>271.7232861003955</v>
@@ -10852,10 +10852,10 @@
         <v>3618.385647774603</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1143.041250161384</v>
+        <v>1143.041250161383</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -10870,13 +10870,13 @@
         <v>1157.115197318205</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>271.4243920631148</v>
+        <v>271.4243920631149</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5068.100277253077</v>
+        <v>5068.100277253076</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -10921,13 +10921,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.965722454756</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3980.972262557945</v>
+        <v>3980.970361894082</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -10939,10 +10939,10 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.014497408322</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4383.105585846696</v>
+        <v>4383.100197657335</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -10951,13 +10951,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>449.3890492690071</v>
+        <v>449.3890492690072</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.04785981867</v>
+        <v>4398.986749732734</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087677</v>
+        <v>4848.375799001741</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -11080,46 +11080,46 @@
         <v>2760.937391194303</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.4849430367736</v>
+        <v>710.4849430367738</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>245.7140354696757</v>
+        <v>245.7140354696758</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>406.9924088095189</v>
+        <v>406.9921954129193</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>4124.128778510271</v>
+        <v>4124.128565113671</v>
       </c>
       <c r="P61" s="130" t="n">
         <v>2896.738881877362</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>758.54766362367</v>
+        <v>758.5476636236698</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>256.0029063005556</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>412.9240454842196</v>
+        <v>412.9234870249217</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4324.213497285807</v>
+        <v>4324.212938826509</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3030.200510783198</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.719726109169</v>
+        <v>802.7197261091691</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7806947937877</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4526.852231508797</v>
+        <v>4526.846288841426</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>825846.3264872718</v>
+        <v>825241.3228158709</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>2581.255131689318</v>
+        <v>2572.722461289518</v>
       </c>
     </row>
     <row r="62">
@@ -11233,55 +11233,55 @@
         <v>229</v>
       </c>
       <c r="G63" s="131" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H63" s="132" t="n">
-        <v>5063</v>
+        <v>5073</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6063.963028375118</v>
+        <v>6063.95385411218</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076215</v>
+        <v>1028.516213076213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>482.4032427834436</v>
+        <v>477.505793182102</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481004</v>
+        <v>2653.723479434723</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10219.64392971578</v>
+        <v>10223.69933980522</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>6897.230573753623</v>
+        <v>6897.219061859658</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1192.650797495556</v>
+        <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.4264574542294</v>
+        <v>513.29853309591</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>2834.005975254689</v>
+        <v>2842.574994921451</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11443.3138039581</v>
+        <v>11445.74338737257</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971947</v>
+        <v>7858.807911385724</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473848</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611685</v>
+        <v>537.0837375110368</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886602</v>
+        <v>3103.122540499337</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12892.15756086994</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>638383.8403829137</v>
+        <v>638383.8403829136</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>215.2831138527744</v>
@@ -11314,10 +11314,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="134" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H64" s="135" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="J64" s="133" t="n">
         <v>0</v>
@@ -11329,10 +11329,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11572,16 +11572,16 @@
         <v>36007.66823156678</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624416</v>
+        <v>5431.185034624418</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>1362.310849873848</v>
+        <v>1362.310135579192</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>44445.04077414373</v>
+        <v>44445.04005984907</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>34052.38752490297</v>
@@ -11590,28 +11590,28 @@
         <v>4646.024039270555</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1463.882211566669</v>
+        <v>1463.88221156667</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>1412.269704923372</v>
+        <v>1412.267794898619</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066356</v>
+        <v>41574.56157063881</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360797</v>
+        <v>33426.99961360798</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183502</v>
+        <v>4250.604456183503</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1620.213936787498</v>
+        <v>1620.19142932314</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355702</v>
+        <v>40672.84056609267</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -11644,55 +11644,55 @@
         <v>3358</v>
       </c>
       <c r="G68" s="143" t="n">
-        <v>6165</v>
+        <v>6175</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>48448</v>
+        <v>48468</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>48409.5719511969</v>
+        <v>48409.56277693396</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>8285.745345589618</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2999.721861871521</v>
+        <v>2994.82441227018</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.03232728299</v>
+        <v>8047.991532881591</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69996.87349981788</v>
+        <v>70009.88811550592</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>47464.74262830856</v>
+        <v>47464.73111641459</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>7740.263750551166</v>
+        <v>7740.263750551165</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2910.660891075922</v>
+        <v>2904.532966717603</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8651.780774253313</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418758</v>
+        <v>69176.53470059541</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>47955.58247823487</v>
+        <v>47955.56872364866</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>7603.582751084724</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326608</v>
+        <v>2899.087602976476</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953928</v>
+        <v>9550.081414348999</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457616</v>
+        <v>70633.91844764759</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -12198,7 +12198,7 @@
         <v>128.2800174617996</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>42.93598052467679</v>
+        <v>42.9359805246768</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>12.1098980688175</v>
@@ -12213,7 +12213,7 @@
         <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13363173601854</v>
+        <v>44.13363173601853</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44747003933478</v>
@@ -12222,13 +12222,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -12271,10 +12271,10 @@
         <v>46.76876318724293</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>293.459219768103</v>
+        <v>293.454975391339</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>340.2279829553459</v>
+        <v>340.2237385785819</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -12286,10 +12286,10 @@
         <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>346.9012428180422</v>
+        <v>346.8954687025169</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>397.9406897215059</v>
+        <v>397.9349156059806</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -12298,13 +12298,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446341</v>
+        <v>55.9139763744634</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>429.6897602068635</v>
+        <v>429.6820421563438</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>485.6037365813269</v>
+        <v>485.5960185308072</v>
       </c>
     </row>
     <row r="78">
@@ -12405,10 +12405,10 @@
         <v>51.20888766333687</v>
       </c>
       <c r="M79" s="131" t="n">
-        <v>6.696987462960856</v>
+        <v>6.696890602695233</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2866.74538671823</v>
+        <v>2866.745289857964</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2967.764433241743</v>
@@ -12420,25 +12420,25 @@
         <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869917</v>
+        <v>7.015452520844691</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907147</v>
+        <v>3178.988967134122</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181512</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>170.896069546928</v>
+        <v>170.8960695469279</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.0050868260645</v>
+        <v>73.00508682606451</v>
       </c>
       <c r="Y79" s="131" t="n">
-        <v>7.392892254635247</v>
+        <v>7.392759464140354</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3496.28003080914</v>
+        <v>3496.279898018644</v>
       </c>
     </row>
     <row r="80">
@@ -12539,10 +12539,10 @@
         <v>197.3705810333049</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>176.0290901661888</v>
+        <v>176.0265442118289</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1576.803216563795</v>
+        <v>1576.800670609435</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>1090.701571439859</v>
@@ -12554,10 +12554,10 @@
         <v>218.5733671538328</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>262.6291555824171</v>
+        <v>262.6247841622621</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1743.814959403218</v>
+        <v>1743.810587983063</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>1148.288930966286</v>
@@ -12569,10 +12569,10 @@
         <v>257.0678553579128</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>346.9079872526063</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1930.5145187721</v>
+        <v>1930.508287640667</v>
       </c>
     </row>
     <row r="82">
@@ -12606,10 +12606,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -12621,10 +12621,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -12636,10 +12636,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
     </row>
     <row r="83">
@@ -12808,13 +12808,13 @@
         <v>251057.4170218568</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557481</v>
+        <v>57266.91038557482</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>969.9340240824498</v>
+        <v>969.9199956752398</v>
       </c>
       <c r="N85" s="141" t="n">
-        <v>1413346.604401443</v>
+        <v>1413346.590373036</v>
       </c>
       <c r="P85" s="139" t="n">
         <v>1115952.652029663</v>
@@ -12826,10 +12826,10 @@
         <v>57819.37211079447</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.62527354356</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427459.890486034</v>
+        <v>1427459.872249224</v>
       </c>
       <c r="V85" s="139" t="n">
         <v>1125695.480763512</v>
@@ -12841,10 +12841,10 @@
         <v>58283.77647998057</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>1183.845442488683</v>
+        <v>1183.824178358655</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1438770.993451629</v>
+        <v>1438770.972187499</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -12878,10 +12878,10 @@
         <v>57574.36851552752</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>1446.119321479702</v>
+        <v>1446.098405881103</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>1418489.735973902</v>
+        <v>1418489.712512349</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>1120142.848455235</v>
@@ -12893,10 +12893,10 @@
         <v>58164.31294237659</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048319</v>
+        <v>1712.160978929183</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1433231.575897314</v>
+        <v>1433231.543026775</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>1130223.153690994</v>
@@ -12908,10 +12908,10 @@
         <v>58682.4705383649</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>1967.836082202788</v>
+        <v>1967.800736100312</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>1445222.459991917</v>
+        <v>1445222.418414683</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13421,7 +13421,7 @@
         <v>1187.174881897402</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -13433,16 +13433,16 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029856</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>284.1315318890079</v>
+        <v>284.131531889008</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125526</v>
       </c>
     </row>
     <row r="95">
@@ -13473,13 +13473,13 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>3918.426842886722</v>
+        <v>3918.420697846095</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4321.200245513292</v>
+        <v>4321.194100472664</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -13491,10 +13491,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.909966110838</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.035113263316</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -13503,13 +13503,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>505.3030256434705</v>
+        <v>505.3030256434706</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025534</v>
+        <v>4828.668791889078</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669004</v>
+        <v>5333.971817532548</v>
       </c>
     </row>
     <row r="96">
@@ -13601,49 +13601,49 @@
         <v>35788</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5457.960764601422</v>
+        <v>5457.960764601421</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>822.3010812215867</v>
+        <v>822.3010812215869</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>296.9229231330126</v>
+        <v>296.9229231330127</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>413.6893962724798</v>
+        <v>413.6890860156146</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>6990.874165228502</v>
+        <v>6990.873854971635</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119106</v>
+        <v>5864.503315119105</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>899.8761975097219</v>
+        <v>899.8761975097217</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>318.8834537860382</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>419.9396147780895</v>
+        <v>419.9389395457664</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192956</v>
+        <v>7503.201905960631</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6275.186492964711</v>
+        <v>6275.18649296471</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560969</v>
+        <v>973.615795656097</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>435.1795297157934</v>
+        <v>435.173454257928</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8023.132262317936</v>
+        <v>8023.12618686007</v>
       </c>
     </row>
     <row r="98">
@@ -13729,55 +13729,55 @@
         <v>292</v>
       </c>
       <c r="G99" s="131" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H99" s="132" t="n">
-        <v>5915</v>
+        <v>5925</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7101.643792012008</v>
+        <v>7101.634617748903</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>674.8763742154042</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647193</v>
+        <v>2829.750023646551</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11800.50001041466</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>7987.932145193219</v>
+        <v>7987.920633299276</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1364.561662722641</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>737.999824608065</v>
+        <v>731.8719002497455</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837106</v>
+        <v>3105.199779083713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>13187.12876336103</v>
+        <v>13189.55397535537</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>9007.110596938059</v>
+        <v>9007.096842351835</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1571.393116669147</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>801.4714782190786</v>
+        <v>794.1515928689478</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139209</v>
+        <v>3450.02429662051</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14821.73831296549</v>
+        <v>14822.66584851044</v>
       </c>
     </row>
     <row r="100">
@@ -13796,10 +13796,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="134" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H100" s="135" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="J100" s="133" t="n">
         <v>0</v>
@@ -13811,10 +13811,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
     </row>
     <row r="101">
@@ -14013,13 +14013,13 @@
         <v>256488.6020564813</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365349</v>
+        <v>58910.7870436535</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>2332.244873956298</v>
+        <v>2332.230131254431</v>
       </c>
       <c r="N103" s="141" t="n">
-        <v>1457791.645175586</v>
+        <v>1457791.630432884</v>
       </c>
       <c r="P103" s="139" t="n">
         <v>1150005.039554566</v>
@@ -14031,10 +14031,10 @@
         <v>59283.25432236114</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.893068442178</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469034.453966697</v>
+        <v>1469034.433819862</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>1159122.48037712</v>
@@ -14046,10 +14046,10 @@
         <v>59658.82154695861</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>2804.059379276181</v>
+        <v>2804.015607681795</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>1479443.856525186</v>
+        <v>1479443.812753592</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -14068,55 +14068,55 @@
         <v>3504</v>
       </c>
       <c r="G104" s="143" t="n">
-        <v>7086</v>
+        <v>7096</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>52114</v>
+        <v>52134</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1156324.899075631</v>
+        <v>1156324.889901368</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>259663.6372678835</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739904</v>
+        <v>60569.1929277977</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762692</v>
+        <v>9494.089938762692</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1488486.609473719</v>
+        <v>1488499.600627854</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1167607.591083543</v>
+        <v>1167607.579571649</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>260689.8596166228</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>61074.97383345251</v>
+        <v>61068.84590909419</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>10355.40908930828</v>
+        <v>10363.9417531825</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1502397.119851501</v>
+        <v>1502408.07772737</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1178178.736169229</v>
+        <v>1178178.722414643</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>261605.6744441866</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61588.87802669151</v>
+        <v>61581.55814134137</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>11509.73965015672</v>
+        <v>11517.88215044931</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1515847.266826493</v>
+        <v>1515856.33686233</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>1578675</v>
+        <v>1578685</v>
       </c>
     </row>
     <row r="109"/>
@@ -15102,19 +15102,19 @@
       </c>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="39" t="n">
-        <v>115791</v>
+        <v>115790</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>2971148.640196562</v>
+        <v>2971146.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2832362</v>
+        <v>2832334</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>25.65958183448249</v>
+        <v>25.65978616630591</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.46098574155159</v>
+        <v>24.46095517747647</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45235826.03390887</v>
+        <v>43489793.39706919</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>57217.44053621583</v>
@@ -15182,13 +15182,13 @@
         <v>23842</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>1864813.399864435</v>
+        <v>1864963.399864435</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>2121209</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>78.21547688383673</v>
+        <v>78.22176830234189</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>88.96942370606493</v>
@@ -15256,19 +15256,19 @@
       </c>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="60" t="n">
-        <v>7921</v>
+        <v>7763</v>
       </c>
       <c r="E27" s="61" t="n">
-        <v>516620.4499400854</v>
+        <v>515166.4499400854</v>
       </c>
       <c r="F27" s="61" t="n">
-        <v>580697</v>
+        <v>568037</v>
       </c>
       <c r="G27" s="62" t="n">
-        <v>65.22161973741768</v>
+        <v>66.36177379107116</v>
       </c>
       <c r="H27" s="63" t="n">
-        <v>73.31107183436434</v>
+        <v>73.17235604791962</v>
       </c>
       <c r="I27" s="31" t="n"/>
       <c r="J27" s="31" t="n"/>
@@ -15333,19 +15333,19 @@
       </c>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="65" t="n">
-        <v>147554</v>
+        <v>147395</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>5352582.490001082</v>
+        <v>5351276.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5534268</v>
+        <v>5521580</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>36.27541435678519</v>
+        <v>36.30568533533079</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.50672973962075</v>
+        <v>37.46110790732386</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -15487,19 +15487,19 @@
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="70" t="n">
-        <v>154536</v>
+        <v>154377</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>5509965.570032656</v>
+        <v>5508659.570032656</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5879288</v>
+        <v>5866600</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>35.65489963524782</v>
+        <v>35.68316245316761</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.04477921002226</v>
+        <v>38.00177487579109</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -15698,19 +15698,19 @@
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="39" t="n">
-        <v>1068917</v>
+        <v>1068918</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>47347727.77691305</v>
+        <v>47347729.77691305</v>
       </c>
       <c r="F33" s="40" t="n">
-        <v>25837092</v>
+        <v>25837120</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>44.29504608581681</v>
+        <v>44.29500651772451</v>
       </c>
       <c r="H33" s="42" t="n">
-        <v>24.17127990292979</v>
+        <v>24.17128348479491</v>
       </c>
       <c r="I33" s="31" t="n"/>
       <c r="J33" s="31" t="n"/>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>4659484.105036949</v>
+        <v>4659484.10503695</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>15724.71578175682</v>
+        <v>15724.71578175683</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15852,19 +15852,19 @@
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="60" t="n">
-        <v>55117</v>
+        <v>55265</v>
       </c>
       <c r="E35" s="61" t="n">
-        <v>5536753.690037966</v>
+        <v>5537597.690037966</v>
       </c>
       <c r="F35" s="61" t="n">
-        <v>4379318</v>
+        <v>4391134</v>
       </c>
       <c r="G35" s="62" t="n">
-        <v>100.4545546752901</v>
+        <v>100.2008086499225</v>
       </c>
       <c r="H35" s="63" t="n">
-        <v>79.4549413066749</v>
+        <v>79.4559667058717</v>
       </c>
       <c r="I35" s="31" t="n"/>
       <c r="J35" s="31" t="n"/>
@@ -15929,19 +15929,19 @@
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="65" t="n">
-        <v>1371213</v>
+        <v>1371362</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>79307125.54702628</v>
+        <v>79307971.54702628</v>
       </c>
       <c r="F36" s="66" t="n">
-        <v>52386298</v>
+        <v>52398142</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>57.83720366349085</v>
+        <v>57.83153649220722</v>
       </c>
       <c r="H36" s="68" t="n">
-        <v>38.20434753754522</v>
+        <v>38.2088332621146</v>
       </c>
       <c r="I36" s="31" t="n"/>
       <c r="J36" s="31" t="n"/>
@@ -16083,19 +16083,19 @@
       </c>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="70" t="n">
-        <v>1372025</v>
+        <v>1372174</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>79351676.9670254</v>
+        <v>79352522.9670254</v>
       </c>
       <c r="F38" s="71" t="n">
-        <v>52413843</v>
+        <v>52425687</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>57.83544539423509</v>
+        <v>57.82978176749115</v>
       </c>
       <c r="H38" s="73" t="n">
-        <v>38.20181337803611</v>
+        <v>38.20629672330185</v>
       </c>
       <c r="I38" s="31" t="n"/>
       <c r="J38" s="31" t="n"/>
@@ -16196,7 +16196,7 @@
         <v>2569858.204487988</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2396.746329438651</v>
+        <v>2396.74632943865</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -16340,7 +16340,7 @@
         <v>1861818.454111506</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>3412.859287341888</v>
+        <v>3412.859287341887</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -16370,13 +16370,13 @@
         <v>271021</v>
       </c>
       <c r="E42" s="51" t="n">
-        <v>28287457.4799397</v>
+        <v>28287607.4799397</v>
       </c>
       <c r="F42" s="51" t="n">
         <v>24291097</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>104.3736739217245</v>
+        <v>104.3742273843713</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>89.62809892960324</v>
@@ -16444,19 +16444,19 @@
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="60" t="n">
-        <v>63038</v>
+        <v>63028</v>
       </c>
       <c r="E43" s="61" t="n">
-        <v>6053374.139978051</v>
+        <v>6052764.139978051</v>
       </c>
       <c r="F43" s="61" t="n">
-        <v>4960015</v>
+        <v>4959171</v>
       </c>
       <c r="G43" s="62" t="n">
-        <v>96.02738253082349</v>
+        <v>96.03293996284272</v>
       </c>
       <c r="H43" s="63" t="n">
-        <v>78.68293727592881</v>
+        <v>78.68203020879609</v>
       </c>
       <c r="I43" s="31" t="n"/>
       <c r="J43" s="31" t="n"/>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1738156.812275141</v>
+        <v>1738156.81227514</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2131.779535882219</v>
@@ -16521,19 +16521,19 @@
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="65" t="n">
-        <v>1518767</v>
+        <v>1518757</v>
       </c>
       <c r="E44" s="66" t="n">
-        <v>84659708.03702736</v>
+        <v>84659248.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57920566</v>
+        <v>57919722</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>55.74239368976766</v>
+        <v>55.74245783692017</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13657131080673</v>
+        <v>38.13626669704239</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -16640,19 +16640,19 @@
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="70" t="n">
-        <v>1526561</v>
+        <v>1526551</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>84861642.53705806</v>
+        <v>84861182.53705806</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58293131</v>
+        <v>58292287</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>55.59007634615194</v>
+        <v>55.59013916800556</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18591657981568</v>
+        <v>38.18561384454237</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -16758,10 +16758,10 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>59315244.66163597</v>
+        <v>57569212.02479628</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>74258.41862736085</v>
+        <v>73705.64703422485</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>5031509.030341239</v>
+        <v>5031509.03034124</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>17288.14627740435</v>
@@ -17361,7 +17361,7 @@
         <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>1115.559154852212</v>
+        <v>1115.559154852213</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>271.7232861003955</v>
@@ -17376,10 +17376,10 @@
         <v>3618.385647774603</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1143.041250161384</v>
+        <v>1143.041250161383</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -17394,13 +17394,13 @@
         <v>1157.115197318205</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>271.4243920631148</v>
+        <v>271.4243920631149</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5068.100277253077</v>
+        <v>5068.100277253076</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -17445,13 +17445,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.965722454756</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3980.972262557945</v>
+        <v>3980.970361894082</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.014497408322</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4383.105585846696</v>
+        <v>4383.100197657335</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -17475,13 +17475,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>449.3890492690071</v>
+        <v>449.3890492690072</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.04785981867</v>
+        <v>4398.986749732734</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087677</v>
+        <v>4848.375799001741</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>884607.9620802102</v>
+        <v>884607.9620802103</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2371.245811243431</v>
@@ -17604,46 +17604,46 @@
         <v>2760.937391194303</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.4849430367736</v>
+        <v>710.4849430367738</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>245.7140354696757</v>
+        <v>245.7140354696758</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>406.9924088095189</v>
+        <v>406.9921954129193</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>4124.128778510271</v>
+        <v>4124.128565113671</v>
       </c>
       <c r="P61" s="130" t="n">
         <v>2896.738881877362</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>758.54766362367</v>
+        <v>758.5476636236698</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>256.0029063005556</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>412.9240454842196</v>
+        <v>412.9234870249217</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4324.213497285807</v>
+        <v>4324.212938826509</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3030.200510783198</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.719726109169</v>
+        <v>802.7197261091691</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7806947937877</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4526.852231508797</v>
+        <v>4526.846288841426</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>839718.9770782276</v>
+        <v>839718.9770782277</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>524.462996491248</v>
@@ -17735,10 +17735,10 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>806618.3115180392</v>
+        <v>806027.7387960516</v>
       </c>
       <c r="AH62" s="56" t="n">
-        <v>2463.75639809482</v>
+        <v>2455.612134851619</v>
       </c>
     </row>
     <row r="63">
@@ -17757,55 +17757,55 @@
         <v>229</v>
       </c>
       <c r="G63" s="131" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H63" s="132" t="n">
-        <v>5063</v>
+        <v>5073</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6063.963028375118</v>
+        <v>6063.95385411218</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076215</v>
+        <v>1028.516213076213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>482.4032427834436</v>
+        <v>477.505793182102</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481004</v>
+        <v>2653.723479434723</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10219.64392971578</v>
+        <v>10223.69933980522</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>6897.230573753623</v>
+        <v>6897.219061859658</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1192.650797495556</v>
+        <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.4264574542294</v>
+        <v>513.29853309591</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>2834.005975254689</v>
+        <v>2842.574994921451</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11443.3138039581</v>
+        <v>11445.74338737257</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971947</v>
+        <v>7858.807911385724</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473848</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611685</v>
+        <v>537.0837375110368</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886602</v>
+        <v>3103.122540499337</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12892.15756086994</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17838,10 +17838,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="134" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H64" s="135" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="J64" s="133" t="n">
         <v>0</v>
@@ -17853,10 +17853,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -18068,7 +18068,7 @@
         <v>440033.7856706333</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>2097.290874083563</v>
+        <v>2097.290874083562</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -18096,16 +18096,16 @@
         <v>36007.66823156678</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624416</v>
+        <v>5431.185034624418</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>1362.310849873848</v>
+        <v>1362.310135579192</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>44445.04077414373</v>
+        <v>44445.04005984907</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>34052.38752490297</v>
@@ -18114,28 +18114,28 @@
         <v>4646.024039270555</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1463.882211566669</v>
+        <v>1463.88221156667</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>1412.269704923372</v>
+        <v>1412.267794898619</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066356</v>
+        <v>41574.56157063881</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360797</v>
+        <v>33426.99961360798</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183502</v>
+        <v>4250.604456183503</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1620.213936787498</v>
+        <v>1620.19142932314</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355702</v>
+        <v>40672.84056609267</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -18168,55 +18168,55 @@
         <v>3358</v>
       </c>
       <c r="G68" s="143" t="n">
-        <v>6165</v>
+        <v>6175</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>48448</v>
+        <v>48468</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>48409.5719511969</v>
+        <v>48409.56277693396</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>8285.745345589618</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2999.721861871521</v>
+        <v>2994.82441227018</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.03232728299</v>
+        <v>8047.991532881591</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69996.87349981788</v>
+        <v>70009.88811550592</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>47464.74262830856</v>
+        <v>47464.73111641459</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>7740.263750551166</v>
+        <v>7740.263750551165</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2910.660891075922</v>
+        <v>2904.532966717603</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8651.780774253313</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418758</v>
+        <v>69176.53470059541</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>47955.58247823487</v>
+        <v>47955.56872364866</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>7603.582751084724</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326608</v>
+        <v>2899.087602976476</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953928</v>
+        <v>9550.081414348999</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457616</v>
+        <v>70633.91844764759</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18722,7 +18722,7 @@
         <v>128.2800174617996</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>42.93598052467679</v>
+        <v>42.9359805246768</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>12.1098980688175</v>
@@ -18737,7 +18737,7 @@
         <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13363173601854</v>
+        <v>44.13363173601853</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44747003933478</v>
@@ -18746,13 +18746,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -18795,10 +18795,10 @@
         <v>46.76876318724293</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>293.459219768103</v>
+        <v>293.454975391339</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>340.2279829553459</v>
+        <v>340.2237385785819</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -18810,10 +18810,10 @@
         <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>346.9012428180422</v>
+        <v>346.8954687025169</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>397.9406897215059</v>
+        <v>397.9349156059806</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -18822,13 +18822,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446341</v>
+        <v>55.9139763744634</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>429.6897602068635</v>
+        <v>429.6820421563438</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>485.6037365813269</v>
+        <v>485.5960185308072</v>
       </c>
     </row>
     <row r="78">
@@ -18929,10 +18929,10 @@
         <v>51.20888766333687</v>
       </c>
       <c r="M79" s="131" t="n">
-        <v>6.696987462960856</v>
+        <v>6.696890602695233</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2866.74538671823</v>
+        <v>2866.745289857964</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2967.764433241743</v>
@@ -18944,25 +18944,25 @@
         <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869917</v>
+        <v>7.015452520844691</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907147</v>
+        <v>3178.988967134122</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181512</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>170.896069546928</v>
+        <v>170.8960695469279</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.0050868260645</v>
+        <v>73.00508682606451</v>
       </c>
       <c r="Y79" s="131" t="n">
-        <v>7.392892254635247</v>
+        <v>7.392759464140354</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3496.28003080914</v>
+        <v>3496.279898018644</v>
       </c>
     </row>
     <row r="80">
@@ -19063,10 +19063,10 @@
         <v>197.3705810333049</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>176.0290901661888</v>
+        <v>176.0265442118289</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1576.803216563795</v>
+        <v>1576.800670609435</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>1090.701571439859</v>
@@ -19078,10 +19078,10 @@
         <v>218.5733671538328</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>262.6291555824171</v>
+        <v>262.6247841622621</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1743.814959403218</v>
+        <v>1743.810587983063</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>1148.288930966286</v>
@@ -19093,10 +19093,10 @@
         <v>257.0678553579128</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>346.9079872526063</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1930.5145187721</v>
+        <v>1930.508287640667</v>
       </c>
     </row>
     <row r="82">
@@ -19130,10 +19130,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -19145,10 +19145,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
     </row>
     <row r="83">
@@ -19332,13 +19332,13 @@
         <v>251057.4170218568</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557481</v>
+        <v>57266.91038557482</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>969.9340240824498</v>
+        <v>969.9199956752398</v>
       </c>
       <c r="N85" s="141" t="n">
-        <v>1413346.604401443</v>
+        <v>1413346.590373036</v>
       </c>
       <c r="P85" s="139" t="n">
         <v>1115952.652029663</v>
@@ -19350,10 +19350,10 @@
         <v>57819.37211079447</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.62527354356</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427459.890486034</v>
+        <v>1427459.872249224</v>
       </c>
       <c r="V85" s="139" t="n">
         <v>1125695.480763512</v>
@@ -19365,10 +19365,10 @@
         <v>58283.77647998057</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>1183.845442488683</v>
+        <v>1183.824178358655</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1438770.993451629</v>
+        <v>1438770.972187499</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -19402,10 +19402,10 @@
         <v>57574.36851552752</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>1446.119321479702</v>
+        <v>1446.098405881103</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>1418489.735973902</v>
+        <v>1418489.712512349</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>1120142.848455235</v>
@@ -19417,10 +19417,10 @@
         <v>58164.31294237659</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048319</v>
+        <v>1712.160978929183</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1433231.575897314</v>
+        <v>1433231.543026775</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>1130223.153690994</v>
@@ -19432,10 +19432,10 @@
         <v>58682.4705383649</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>1967.836082202788</v>
+        <v>1967.800736100312</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>1445222.459991917</v>
+        <v>1445222.418414683</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19945,7 +19945,7 @@
         <v>1187.174881897402</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -19957,16 +19957,16 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029856</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>284.1315318890079</v>
+        <v>284.131531889008</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125526</v>
       </c>
     </row>
     <row r="95">
@@ -19997,13 +19997,13 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>3918.426842886722</v>
+        <v>3918.420697846095</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4321.200245513292</v>
+        <v>4321.194100472664</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -20015,10 +20015,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.909966110838</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.035113263316</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -20027,13 +20027,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>505.3030256434705</v>
+        <v>505.3030256434706</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025534</v>
+        <v>4828.668791889078</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669004</v>
+        <v>5333.971817532548</v>
       </c>
     </row>
     <row r="96">
@@ -20125,49 +20125,49 @@
         <v>35788</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5457.960764601422</v>
+        <v>5457.960764601421</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>822.3010812215867</v>
+        <v>822.3010812215869</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>296.9229231330126</v>
+        <v>296.9229231330127</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>413.6893962724798</v>
+        <v>413.6890860156146</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>6990.874165228502</v>
+        <v>6990.873854971635</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119106</v>
+        <v>5864.503315119105</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>899.8761975097219</v>
+        <v>899.8761975097217</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>318.8834537860382</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>419.9396147780895</v>
+        <v>419.9389395457664</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192956</v>
+        <v>7503.201905960631</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6275.186492964711</v>
+        <v>6275.18649296471</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560969</v>
+        <v>973.615795656097</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>435.1795297157934</v>
+        <v>435.173454257928</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8023.132262317936</v>
+        <v>8023.12618686007</v>
       </c>
     </row>
     <row r="98">
@@ -20253,55 +20253,55 @@
         <v>292</v>
       </c>
       <c r="G99" s="131" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H99" s="132" t="n">
-        <v>5915</v>
+        <v>5925</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7101.643792012008</v>
+        <v>7101.634617748903</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>674.8763742154042</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647193</v>
+        <v>2829.750023646551</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11800.50001041466</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>7987.932145193219</v>
+        <v>7987.920633299276</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1364.561662722641</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>737.999824608065</v>
+        <v>731.8719002497455</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837106</v>
+        <v>3105.199779083713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>13187.12876336103</v>
+        <v>13189.55397535537</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>9007.110596938059</v>
+        <v>9007.096842351835</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1571.393116669147</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>801.4714782190786</v>
+        <v>794.1515928689478</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139209</v>
+        <v>3450.02429662051</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14821.73831296549</v>
+        <v>14822.66584851044</v>
       </c>
     </row>
     <row r="100">
@@ -20320,10 +20320,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="134" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H100" s="135" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="J100" s="133" t="n">
         <v>0</v>
@@ -20335,10 +20335,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20365,10 +20365,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
     </row>
     <row r="101">
@@ -20537,13 +20537,13 @@
         <v>256488.6020564813</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365349</v>
+        <v>58910.7870436535</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>2332.244873956298</v>
+        <v>2332.230131254431</v>
       </c>
       <c r="N103" s="141" t="n">
-        <v>1457791.645175586</v>
+        <v>1457791.630432884</v>
       </c>
       <c r="P103" s="139" t="n">
         <v>1150005.039554566</v>
@@ -20555,10 +20555,10 @@
         <v>59283.25432236114</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.893068442178</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469034.453966697</v>
+        <v>1469034.433819862</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>1159122.48037712</v>
@@ -20570,10 +20570,10 @@
         <v>59658.82154695861</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>2804.059379276181</v>
+        <v>2804.015607681795</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>1479443.856525186</v>
+        <v>1479443.812753592</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -20592,55 +20592,55 @@
         <v>3504</v>
       </c>
       <c r="G104" s="143" t="n">
-        <v>7086</v>
+        <v>7096</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>52114</v>
+        <v>52134</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1156324.899075631</v>
+        <v>1156324.889901368</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>259663.6372678835</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739904</v>
+        <v>60569.1929277977</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762692</v>
+        <v>9494.089938762692</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1488486.609473719</v>
+        <v>1488499.600627854</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1167607.591083543</v>
+        <v>1167607.579571649</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>260689.8596166228</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>61074.97383345251</v>
+        <v>61068.84590909419</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>10355.40908930828</v>
+        <v>10363.9417531825</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1502397.119851501</v>
+        <v>1502408.07772737</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1178178.736169229</v>
+        <v>1178178.722414643</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>261605.6744441866</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61588.87802669151</v>
+        <v>61581.55814134137</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>11509.73965015672</v>
+        <v>11517.88215044931</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1515847.266826493</v>
+        <v>1515856.33686233</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -20662,7 +20662,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>1578675</v>
+        <v>1578685</v>
       </c>
     </row>
     <row r="109"/>
@@ -21626,19 +21626,19 @@
       </c>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="39" t="n">
-        <v>115791</v>
+        <v>115790</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>2971148.640196562</v>
+        <v>2971146.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2832362</v>
+        <v>2832334</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>25.65958183448249</v>
+        <v>25.65978616630591</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.46098574155159</v>
+        <v>24.46095517747647</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -21706,13 +21706,13 @@
         <v>23842</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>1864813.399864435</v>
+        <v>1864963.399864435</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>2121209</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>78.21547688383673</v>
+        <v>78.22176830234189</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>88.96942370606493</v>
@@ -21780,19 +21780,19 @@
       </c>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="60" t="n">
-        <v>7921</v>
+        <v>7763</v>
       </c>
       <c r="E27" s="61" t="n">
-        <v>516620.4499400854</v>
+        <v>515166.4499400854</v>
       </c>
       <c r="F27" s="61" t="n">
-        <v>580697</v>
+        <v>568037</v>
       </c>
       <c r="G27" s="62" t="n">
-        <v>65.22161973741768</v>
+        <v>66.36177379107116</v>
       </c>
       <c r="H27" s="63" t="n">
-        <v>73.31107183436434</v>
+        <v>73.17235604791962</v>
       </c>
       <c r="I27" s="31" t="n"/>
       <c r="J27" s="31" t="n"/>
@@ -21857,19 +21857,19 @@
       </c>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="65" t="n">
-        <v>147554</v>
+        <v>147395</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>5352582.490001082</v>
+        <v>5351276.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5534268</v>
+        <v>5521580</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>36.27541435678519</v>
+        <v>36.30568533533079</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.50672973962075</v>
+        <v>37.46110790732386</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -22011,19 +22011,19 @@
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="70" t="n">
-        <v>154536</v>
+        <v>154377</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>5509965.570032656</v>
+        <v>5508659.570032656</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5879288</v>
+        <v>5866600</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>35.65489963524782</v>
+        <v>35.68316245316761</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.04477921002226</v>
+        <v>38.00177487579109</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -22195,7 +22195,7 @@
         <v>6216688.077260031</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>801.3791921122271</v>
+        <v>801.3791921122272</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22222,19 +22222,19 @@
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="39" t="n">
-        <v>1068917</v>
+        <v>1068918</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>47347727.77691305</v>
+        <v>47347729.77691305</v>
       </c>
       <c r="F33" s="40" t="n">
-        <v>25837092</v>
+        <v>25837120</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>44.29504608581681</v>
+        <v>44.29500651772451</v>
       </c>
       <c r="H33" s="42" t="n">
-        <v>24.17127990292979</v>
+        <v>24.17128348479491</v>
       </c>
       <c r="I33" s="31" t="n"/>
       <c r="J33" s="31" t="n"/>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5310405.84253849</v>
+        <v>5310405.842538491</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>17641.43818058407</v>
@@ -22376,19 +22376,19 @@
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="60" t="n">
-        <v>55117</v>
+        <v>55265</v>
       </c>
       <c r="E35" s="61" t="n">
-        <v>5536753.690037966</v>
+        <v>5537597.690037966</v>
       </c>
       <c r="F35" s="61" t="n">
-        <v>4379318</v>
+        <v>4391134</v>
       </c>
       <c r="G35" s="62" t="n">
-        <v>100.4545546752901</v>
+        <v>100.2008086499225</v>
       </c>
       <c r="H35" s="63" t="n">
-        <v>79.4549413066749</v>
+        <v>79.4559667058717</v>
       </c>
       <c r="I35" s="31" t="n"/>
       <c r="J35" s="31" t="n"/>
@@ -22453,19 +22453,19 @@
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="65" t="n">
-        <v>1371213</v>
+        <v>1371362</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>79307125.54702628</v>
+        <v>79307971.54702628</v>
       </c>
       <c r="F36" s="66" t="n">
-        <v>52386298</v>
+        <v>52398142</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>57.83720366349085</v>
+        <v>57.83153649220722</v>
       </c>
       <c r="H36" s="68" t="n">
-        <v>38.20434753754522</v>
+        <v>38.2088332621146</v>
       </c>
       <c r="I36" s="31" t="n"/>
       <c r="J36" s="31" t="n"/>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3690548.339654155</v>
+        <v>3690548.339654154</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>11271.648789632</v>
@@ -22607,19 +22607,19 @@
       </c>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="70" t="n">
-        <v>1372025</v>
+        <v>1372174</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>79351676.9670254</v>
+        <v>79352522.9670254</v>
       </c>
       <c r="F38" s="71" t="n">
-        <v>52413843</v>
+        <v>52425687</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>57.83544539423509</v>
+        <v>57.82978176749115</v>
       </c>
       <c r="H38" s="73" t="n">
-        <v>38.20181337803611</v>
+        <v>38.20629672330185</v>
       </c>
       <c r="I38" s="31" t="n"/>
       <c r="J38" s="31" t="n"/>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2918129.028513301</v>
+        <v>2918129.028513302</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2574.249362596877</v>
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2029241.191294712</v>
+        <v>2029241.191294711</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>3570.123843302602</v>
@@ -22894,13 +22894,13 @@
         <v>271021</v>
       </c>
       <c r="E42" s="51" t="n">
-        <v>28287457.4799397</v>
+        <v>28287607.4799397</v>
       </c>
       <c r="F42" s="51" t="n">
         <v>24291097</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>104.3736739217245</v>
+        <v>104.3742273843713</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>89.62809892960324</v>
@@ -22968,19 +22968,19 @@
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="60" t="n">
-        <v>63038</v>
+        <v>63028</v>
       </c>
       <c r="E43" s="61" t="n">
-        <v>6053374.139978051</v>
+        <v>6052764.139978051</v>
       </c>
       <c r="F43" s="61" t="n">
-        <v>4960015</v>
+        <v>4959171</v>
       </c>
       <c r="G43" s="62" t="n">
-        <v>96.02738253082349</v>
+        <v>96.03293996284272</v>
       </c>
       <c r="H43" s="63" t="n">
-        <v>78.68293727592881</v>
+        <v>78.68203020879609</v>
       </c>
       <c r="I43" s="31" t="n"/>
       <c r="J43" s="31" t="n"/>
@@ -23045,19 +23045,19 @@
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="65" t="n">
-        <v>1518767</v>
+        <v>1518757</v>
       </c>
       <c r="E44" s="66" t="n">
-        <v>84659708.03702736</v>
+        <v>84659248.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57920566</v>
+        <v>57919722</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>55.74239368976766</v>
+        <v>55.74245783692017</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13657131080673</v>
+        <v>38.13626669704239</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -23164,19 +23164,19 @@
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="70" t="n">
-        <v>1526561</v>
+        <v>1526551</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>84861642.53705806</v>
+        <v>84861182.53705806</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58293131</v>
+        <v>58292287</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>55.59007634615194</v>
+        <v>55.59013916800556</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18591657981568</v>
+        <v>38.18561384454237</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -23285,7 +23285,7 @@
         <v>69779636.95560461</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>85020.26381129169</v>
+        <v>84356.93789952848</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -23885,7 +23885,7 @@
         <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>1115.559154852212</v>
+        <v>1115.559154852213</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>271.7232861003955</v>
@@ -23900,10 +23900,10 @@
         <v>3618.385647774603</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1143.041250161384</v>
+        <v>1143.041250161383</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -23918,13 +23918,13 @@
         <v>1157.115197318205</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>271.4243920631148</v>
+        <v>271.4243920631149</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5068.100277253077</v>
+        <v>5068.100277253076</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -23969,13 +23969,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.965722454756</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3980.972262557945</v>
+        <v>3980.970361894082</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -23987,10 +23987,10 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.014497408322</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4383.105585846696</v>
+        <v>4383.100197657335</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -23999,13 +23999,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>449.3890492690071</v>
+        <v>449.3890492690072</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.04785981867</v>
+        <v>4398.986749732734</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087677</v>
+        <v>4848.375799001741</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -24128,46 +24128,46 @@
         <v>2760.937391194303</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.4849430367736</v>
+        <v>710.4849430367738</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>245.7140354696757</v>
+        <v>245.7140354696758</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>406.9924088095189</v>
+        <v>406.9921954129193</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>4124.128778510271</v>
+        <v>4124.128565113671</v>
       </c>
       <c r="P61" s="130" t="n">
         <v>2896.738881877362</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>758.54766362367</v>
+        <v>758.5476636236698</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>256.0029063005556</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>412.9240454842196</v>
+        <v>412.9234870249217</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4324.213497285807</v>
+        <v>4324.212938826509</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3030.200510783198</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.719726109169</v>
+        <v>802.7197261091691</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7806947937877</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4526.852231508797</v>
+        <v>4526.846288841426</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -24178,10 +24178,10 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>781605.0418458922</v>
+        <v>781033.1019742342</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>2348.723611867773</v>
+        <v>2340.959604275397</v>
       </c>
     </row>
     <row r="62">
@@ -24281,55 +24281,55 @@
         <v>229</v>
       </c>
       <c r="G63" s="131" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H63" s="132" t="n">
-        <v>5063</v>
+        <v>5073</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6063.963028375118</v>
+        <v>6063.95385411218</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076215</v>
+        <v>1028.516213076213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>482.4032427834436</v>
+        <v>477.505793182102</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481004</v>
+        <v>2653.723479434723</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10219.64392971578</v>
+        <v>10223.69933980522</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>6897.230573753623</v>
+        <v>6897.219061859658</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1192.650797495556</v>
+        <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.4264574542294</v>
+        <v>513.29853309591</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>2834.005975254689</v>
+        <v>2842.574994921451</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11443.3138039581</v>
+        <v>11445.74338737257</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971947</v>
+        <v>7858.807911385724</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473848</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611685</v>
+        <v>537.0837375110368</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886602</v>
+        <v>3103.122540499337</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12892.15756086994</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24362,10 +24362,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="134" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H64" s="135" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="J64" s="133" t="n">
         <v>0</v>
@@ -24377,10 +24377,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>412584.2450424845</v>
+        <v>412584.2450424846</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>765.5054408154472</v>
@@ -24620,16 +24620,16 @@
         <v>36007.66823156678</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624416</v>
+        <v>5431.185034624418</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>1362.310849873848</v>
+        <v>1362.310135579192</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>44445.04077414373</v>
+        <v>44445.04005984907</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>34052.38752490297</v>
@@ -24638,28 +24638,28 @@
         <v>4646.024039270555</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1463.882211566669</v>
+        <v>1463.88221156667</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>1412.269704923372</v>
+        <v>1412.267794898619</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066356</v>
+        <v>41574.56157063881</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360797</v>
+        <v>33426.99961360798</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183502</v>
+        <v>4250.604456183503</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1620.213936787498</v>
+        <v>1620.19142932314</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355702</v>
+        <v>40672.84056609267</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -24673,7 +24673,7 @@
         <v>334190.0867178393</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>913.0841014375312</v>
+        <v>913.0841014375313</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24692,55 +24692,55 @@
         <v>3358</v>
       </c>
       <c r="G68" s="143" t="n">
-        <v>6165</v>
+        <v>6175</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>48448</v>
+        <v>48468</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>48409.5719511969</v>
+        <v>48409.56277693396</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>8285.745345589618</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2999.721861871521</v>
+        <v>2994.82441227018</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.03232728299</v>
+        <v>8047.991532881591</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69996.87349981788</v>
+        <v>70009.88811550592</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>47464.74262830856</v>
+        <v>47464.73111641459</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>7740.263750551166</v>
+        <v>7740.263750551165</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2910.660891075922</v>
+        <v>2904.532966717603</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8651.780774253313</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418758</v>
+        <v>69176.53470059541</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>47955.58247823487</v>
+        <v>47955.56872364866</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>7603.582751084724</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326608</v>
+        <v>2899.087602976476</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953928</v>
+        <v>9550.081414348999</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457616</v>
+        <v>70633.91844764759</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -25246,7 +25246,7 @@
         <v>128.2800174617996</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>42.93598052467679</v>
+        <v>42.9359805246768</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>12.1098980688175</v>
@@ -25261,7 +25261,7 @@
         <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13363173601854</v>
+        <v>44.13363173601853</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44747003933478</v>
@@ -25270,13 +25270,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -25319,10 +25319,10 @@
         <v>46.76876318724293</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>293.459219768103</v>
+        <v>293.454975391339</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>340.2279829553459</v>
+        <v>340.2237385785819</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -25334,10 +25334,10 @@
         <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>346.9012428180422</v>
+        <v>346.8954687025169</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>397.9406897215059</v>
+        <v>397.9349156059806</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -25346,13 +25346,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446341</v>
+        <v>55.9139763744634</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>429.6897602068635</v>
+        <v>429.6820421563438</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>485.6037365813269</v>
+        <v>485.5960185308072</v>
       </c>
     </row>
     <row r="78">
@@ -25453,10 +25453,10 @@
         <v>51.20888766333687</v>
       </c>
       <c r="M79" s="131" t="n">
-        <v>6.696987462960856</v>
+        <v>6.696890602695233</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2866.74538671823</v>
+        <v>2866.745289857964</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2967.764433241743</v>
@@ -25468,25 +25468,25 @@
         <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869917</v>
+        <v>7.015452520844691</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907147</v>
+        <v>3178.988967134122</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181512</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>170.896069546928</v>
+        <v>170.8960695469279</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.0050868260645</v>
+        <v>73.00508682606451</v>
       </c>
       <c r="Y79" s="131" t="n">
-        <v>7.392892254635247</v>
+        <v>7.392759464140354</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3496.28003080914</v>
+        <v>3496.279898018644</v>
       </c>
     </row>
     <row r="80">
@@ -25587,10 +25587,10 @@
         <v>197.3705810333049</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>176.0290901661888</v>
+        <v>176.0265442118289</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1576.803216563795</v>
+        <v>1576.800670609435</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>1090.701571439859</v>
@@ -25602,10 +25602,10 @@
         <v>218.5733671538328</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>262.6291555824171</v>
+        <v>262.6247841622621</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1743.814959403218</v>
+        <v>1743.810587983063</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>1148.288930966286</v>
@@ -25617,10 +25617,10 @@
         <v>257.0678553579128</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>346.9079872526063</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1930.5145187721</v>
+        <v>1930.508287640667</v>
       </c>
     </row>
     <row r="82">
@@ -25654,10 +25654,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -25669,10 +25669,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -25684,10 +25684,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
     </row>
     <row r="83">
@@ -25856,13 +25856,13 @@
         <v>251057.4170218568</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557481</v>
+        <v>57266.91038557482</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>969.9340240824498</v>
+        <v>969.9199956752398</v>
       </c>
       <c r="N85" s="141" t="n">
-        <v>1413346.604401443</v>
+        <v>1413346.590373036</v>
       </c>
       <c r="P85" s="139" t="n">
         <v>1115952.652029663</v>
@@ -25874,10 +25874,10 @@
         <v>57819.37211079447</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.62527354356</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427459.890486034</v>
+        <v>1427459.872249224</v>
       </c>
       <c r="V85" s="139" t="n">
         <v>1125695.480763512</v>
@@ -25889,10 +25889,10 @@
         <v>58283.77647998057</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>1183.845442488683</v>
+        <v>1183.824178358655</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1438770.993451629</v>
+        <v>1438770.972187499</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -25926,10 +25926,10 @@
         <v>57574.36851552752</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>1446.119321479702</v>
+        <v>1446.098405881103</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>1418489.735973902</v>
+        <v>1418489.712512349</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>1120142.848455235</v>
@@ -25941,10 +25941,10 @@
         <v>58164.31294237659</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048319</v>
+        <v>1712.160978929183</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1433231.575897314</v>
+        <v>1433231.543026775</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>1130223.153690994</v>
@@ -25956,10 +25956,10 @@
         <v>58682.4705383649</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>1967.836082202788</v>
+        <v>1967.800736100312</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>1445222.459991917</v>
+        <v>1445222.418414683</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26469,7 +26469,7 @@
         <v>1187.174881897402</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -26481,16 +26481,16 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029856</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>284.1315318890079</v>
+        <v>284.131531889008</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125526</v>
       </c>
     </row>
     <row r="95">
@@ -26521,13 +26521,13 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>3918.426842886722</v>
+        <v>3918.420697846095</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4321.200245513292</v>
+        <v>4321.194100472664</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -26539,10 +26539,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.909966110838</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.035113263316</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -26551,13 +26551,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>505.3030256434705</v>
+        <v>505.3030256434706</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025534</v>
+        <v>4828.668791889078</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669004</v>
+        <v>5333.971817532548</v>
       </c>
     </row>
     <row r="96">
@@ -26649,49 +26649,49 @@
         <v>35788</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5457.960764601422</v>
+        <v>5457.960764601421</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>822.3010812215867</v>
+        <v>822.3010812215869</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>296.9229231330126</v>
+        <v>296.9229231330127</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>413.6893962724798</v>
+        <v>413.6890860156146</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>6990.874165228502</v>
+        <v>6990.873854971635</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119106</v>
+        <v>5864.503315119105</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>899.8761975097219</v>
+        <v>899.8761975097217</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>318.8834537860382</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>419.9396147780895</v>
+        <v>419.9389395457664</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192956</v>
+        <v>7503.201905960631</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6275.186492964711</v>
+        <v>6275.18649296471</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560969</v>
+        <v>973.615795656097</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>435.1795297157934</v>
+        <v>435.173454257928</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8023.132262317936</v>
+        <v>8023.12618686007</v>
       </c>
     </row>
     <row r="98">
@@ -26777,55 +26777,55 @@
         <v>292</v>
       </c>
       <c r="G99" s="131" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H99" s="132" t="n">
-        <v>5915</v>
+        <v>5925</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7101.643792012008</v>
+        <v>7101.634617748903</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>674.8763742154042</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647193</v>
+        <v>2829.750023646551</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11800.50001041466</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>7987.932145193219</v>
+        <v>7987.920633299276</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1364.561662722641</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>737.999824608065</v>
+        <v>731.8719002497455</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837106</v>
+        <v>3105.199779083713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>13187.12876336103</v>
+        <v>13189.55397535537</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>9007.110596938059</v>
+        <v>9007.096842351835</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1571.393116669147</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>801.4714782190786</v>
+        <v>794.1515928689478</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139209</v>
+        <v>3450.02429662051</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14821.73831296549</v>
+        <v>14822.66584851044</v>
       </c>
     </row>
     <row r="100">
@@ -26844,10 +26844,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="134" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H100" s="135" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="J100" s="133" t="n">
         <v>0</v>
@@ -26859,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
     </row>
     <row r="101">
@@ -27061,13 +27061,13 @@
         <v>256488.6020564813</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365349</v>
+        <v>58910.7870436535</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>2332.244873956298</v>
+        <v>2332.230131254431</v>
       </c>
       <c r="N103" s="141" t="n">
-        <v>1457791.645175586</v>
+        <v>1457791.630432884</v>
       </c>
       <c r="P103" s="139" t="n">
         <v>1150005.039554566</v>
@@ -27079,10 +27079,10 @@
         <v>59283.25432236114</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.893068442178</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469034.453966697</v>
+        <v>1469034.433819862</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>1159122.48037712</v>
@@ -27094,10 +27094,10 @@
         <v>59658.82154695861</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>2804.059379276181</v>
+        <v>2804.015607681795</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>1479443.856525186</v>
+        <v>1479443.812753592</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -27116,55 +27116,55 @@
         <v>3504</v>
       </c>
       <c r="G104" s="143" t="n">
-        <v>7086</v>
+        <v>7096</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>52114</v>
+        <v>52134</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1156324.899075631</v>
+        <v>1156324.889901368</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>259663.6372678835</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739904</v>
+        <v>60569.1929277977</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762692</v>
+        <v>9494.089938762692</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1488486.609473719</v>
+        <v>1488499.600627854</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1167607.591083543</v>
+        <v>1167607.579571649</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>260689.8596166228</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>61074.97383345251</v>
+        <v>61068.84590909419</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>10355.40908930828</v>
+        <v>10363.9417531825</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1502397.119851501</v>
+        <v>1502408.07772737</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1178178.736169229</v>
+        <v>1178178.722414643</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>261605.6744441866</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61588.87802669151</v>
+        <v>61581.55814134137</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>11509.73965015672</v>
+        <v>11517.88215044931</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1515847.266826493</v>
+        <v>1515856.33686233</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -27186,7 +27186,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>1578675</v>
+        <v>1578685</v>
       </c>
     </row>
     <row r="109"/>
@@ -28150,19 +28150,19 @@
       </c>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="39" t="n">
-        <v>115791</v>
+        <v>115790</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>2971148.640196562</v>
+        <v>2971146.640196562</v>
       </c>
       <c r="F25" s="40" t="n">
-        <v>2832362</v>
+        <v>2832334</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>25.65958183448249</v>
+        <v>25.65978616630591</v>
       </c>
       <c r="H25" s="42" t="n">
-        <v>24.46098574155159</v>
+        <v>24.46095517747647</v>
       </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
@@ -28200,7 +28200,7 @@
         <v>69285584.18914482</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28230,13 +28230,13 @@
         <v>23842</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>1864813.399864435</v>
+        <v>1864963.399864435</v>
       </c>
       <c r="F26" s="51" t="n">
         <v>2121209</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>78.21547688383673</v>
+        <v>78.22176830234189</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>88.96942370606493</v>
@@ -28304,19 +28304,19 @@
       </c>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="60" t="n">
-        <v>7921</v>
+        <v>7763</v>
       </c>
       <c r="E27" s="61" t="n">
-        <v>516620.4499400854</v>
+        <v>515166.4499400854</v>
       </c>
       <c r="F27" s="61" t="n">
-        <v>580697</v>
+        <v>568037</v>
       </c>
       <c r="G27" s="62" t="n">
-        <v>65.22161973741768</v>
+        <v>66.36177379107116</v>
       </c>
       <c r="H27" s="63" t="n">
-        <v>73.31107183436434</v>
+        <v>73.17235604791962</v>
       </c>
       <c r="I27" s="31" t="n"/>
       <c r="J27" s="31" t="n"/>
@@ -28381,19 +28381,19 @@
       </c>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="65" t="n">
-        <v>147554</v>
+        <v>147395</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>5352582.490001082</v>
+        <v>5351276.490001082</v>
       </c>
       <c r="F28" s="66" t="n">
-        <v>5534268</v>
+        <v>5521580</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>36.27541435678519</v>
+        <v>36.30568533533079</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>37.50672973962075</v>
+        <v>37.46110790732386</v>
       </c>
       <c r="I28" s="31" t="n"/>
       <c r="J28" s="31" t="n"/>
@@ -28447,7 +28447,7 @@
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>418.9450962243399</v>
+        <v>418.9450962243398</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -28535,19 +28535,19 @@
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="70" t="n">
-        <v>154536</v>
+        <v>154377</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>5509965.570032656</v>
+        <v>5508659.570032656</v>
       </c>
       <c r="F30" s="71" t="n">
-        <v>5879288</v>
+        <v>5866600</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>35.65489963524782</v>
+        <v>35.68316245316761</v>
       </c>
       <c r="H30" s="73" t="n">
-        <v>38.04477921002226</v>
+        <v>38.00177487579109</v>
       </c>
       <c r="I30" s="31" t="n"/>
       <c r="J30" s="31" t="n"/>
@@ -28746,19 +28746,19 @@
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="39" t="n">
-        <v>1068917</v>
+        <v>1068918</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>47347727.77691305</v>
+        <v>47347729.77691305</v>
       </c>
       <c r="F33" s="40" t="n">
-        <v>25837092</v>
+        <v>25837120</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>44.29504608581681</v>
+        <v>44.29500651772451</v>
       </c>
       <c r="H33" s="42" t="n">
-        <v>24.17127990292979</v>
+        <v>24.17128348479491</v>
       </c>
       <c r="I33" s="31" t="n"/>
       <c r="J33" s="31" t="n"/>
@@ -28796,7 +28796,7 @@
         <v>6674173.389488898</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>11760.22606198546</v>
+        <v>11760.22606198545</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>6109904.890164006</v>
+        <v>6109904.890164007</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28900,19 +28900,19 @@
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="60" t="n">
-        <v>55117</v>
+        <v>55265</v>
       </c>
       <c r="E35" s="61" t="n">
-        <v>5536753.690037966</v>
+        <v>5537597.690037966</v>
       </c>
       <c r="F35" s="61" t="n">
-        <v>4379318</v>
+        <v>4391134</v>
       </c>
       <c r="G35" s="62" t="n">
-        <v>100.4545546752901</v>
+        <v>100.2008086499225</v>
       </c>
       <c r="H35" s="63" t="n">
-        <v>79.4549413066749</v>
+        <v>79.4559667058717</v>
       </c>
       <c r="I35" s="31" t="n"/>
       <c r="J35" s="31" t="n"/>
@@ -28977,19 +28977,19 @@
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="65" t="n">
-        <v>1371213</v>
+        <v>1371362</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>79307125.54702628</v>
+        <v>79307971.54702628</v>
       </c>
       <c r="F36" s="66" t="n">
-        <v>52386298</v>
+        <v>52398142</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>57.83720366349085</v>
+        <v>57.83153649220722</v>
       </c>
       <c r="H36" s="68" t="n">
-        <v>38.20434753754522</v>
+        <v>38.2088332621146</v>
       </c>
       <c r="I36" s="31" t="n"/>
       <c r="J36" s="31" t="n"/>
@@ -29131,19 +29131,19 @@
       </c>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="70" t="n">
-        <v>1372025</v>
+        <v>1372174</v>
       </c>
       <c r="E38" s="71" t="n">
-        <v>79351676.9670254</v>
+        <v>79352522.9670254</v>
       </c>
       <c r="F38" s="71" t="n">
-        <v>52413843</v>
+        <v>52425687</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>57.83544539423509</v>
+        <v>57.82978176749115</v>
       </c>
       <c r="H38" s="73" t="n">
-        <v>38.20181337803611</v>
+        <v>38.20629672330185</v>
       </c>
       <c r="I38" s="31" t="n"/>
       <c r="J38" s="31" t="n"/>
@@ -29385,10 +29385,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2261110.921757243</v>
+        <v>2261110.921757244</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>2957.226786839573</v>
+        <v>2957.226786839572</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -29418,13 +29418,13 @@
         <v>271021</v>
       </c>
       <c r="E42" s="51" t="n">
-        <v>28287457.4799397</v>
+        <v>28287607.4799397</v>
       </c>
       <c r="F42" s="51" t="n">
         <v>24291097</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>104.3736739217245</v>
+        <v>104.3742273843713</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>89.62809892960324</v>
@@ -29492,19 +29492,19 @@
       </c>
       <c r="C43" s="10" t="n"/>
       <c r="D43" s="60" t="n">
-        <v>63038</v>
+        <v>63028</v>
       </c>
       <c r="E43" s="61" t="n">
-        <v>6053374.139978051</v>
+        <v>6052764.139978051</v>
       </c>
       <c r="F43" s="61" t="n">
-        <v>4960015</v>
+        <v>4959171</v>
       </c>
       <c r="G43" s="62" t="n">
-        <v>96.02738253082349</v>
+        <v>96.03293996284272</v>
       </c>
       <c r="H43" s="63" t="n">
-        <v>78.68293727592881</v>
+        <v>78.68203020879609</v>
       </c>
       <c r="I43" s="31" t="n"/>
       <c r="J43" s="31" t="n"/>
@@ -29558,7 +29558,7 @@
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>168.8848225433526</v>
+        <v>168.8848225433525</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -29569,19 +29569,19 @@
       </c>
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="65" t="n">
-        <v>1518767</v>
+        <v>1518757</v>
       </c>
       <c r="E44" s="66" t="n">
-        <v>84659708.03702736</v>
+        <v>84659248.03702736</v>
       </c>
       <c r="F44" s="66" t="n">
-        <v>57920566</v>
+        <v>57919722</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>55.74239368976766</v>
+        <v>55.74245783692017</v>
       </c>
       <c r="H44" s="68" t="n">
-        <v>38.13657131080673</v>
+        <v>38.13626669704239</v>
       </c>
       <c r="I44" s="31" t="n"/>
       <c r="J44" s="31" t="n"/>
@@ -29688,19 +29688,19 @@
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="70" t="n">
-        <v>1526561</v>
+        <v>1526551</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>84861642.53705806</v>
+        <v>84861182.53705806</v>
       </c>
       <c r="F46" s="71" t="n">
-        <v>58293131</v>
+        <v>58292287</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>55.59007634615194</v>
+        <v>55.59013916800556</v>
       </c>
       <c r="H46" s="73" t="n">
-        <v>38.18591657981568</v>
+        <v>38.18561384454237</v>
       </c>
       <c r="I46" s="31" t="n"/>
       <c r="J46" s="31" t="n"/>
@@ -29809,7 +29809,7 @@
         <v>83449597.02281936</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>98089.90734281891</v>
+        <v>97293.91624870307</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -29855,7 +29855,7 @@
         <v>17497628.15572617</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>7416.433009064743</v>
+        <v>7416.433009064744</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -30409,7 +30409,7 @@
         <v>3577.0033000607</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>1115.559154852212</v>
+        <v>1115.559154852213</v>
       </c>
       <c r="L58" s="131" t="n">
         <v>271.7232861003955</v>
@@ -30424,10 +30424,10 @@
         <v>3618.385647774603</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>1143.041250161384</v>
+        <v>1143.041250161383</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>272.2636155054546</v>
+        <v>272.2636155054545</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -30442,13 +30442,13 @@
         <v>1157.115197318205</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>271.4243920631148</v>
+        <v>271.4243920631149</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5068.100277253077</v>
+        <v>5068.100277253076</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1648512.402877569</v>
+        <v>1648512.40287757</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>3969.264717832511</v>
@@ -30493,13 +30493,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>356.0046394393262</v>
+        <v>356.0046394393264</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>3624.967623118619</v>
+        <v>3624.965722454756</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3980.972262557945</v>
+        <v>3980.970361894082</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -30511,10 +30511,10 @@
         <v>399.0857002490135</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>3984.019885597682</v>
+        <v>3984.014497408322</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4383.105585846696</v>
+        <v>4383.100197657335</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -30523,13 +30523,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>449.3890492690071</v>
+        <v>449.3890492690072</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4399.04785981867</v>
+        <v>4398.986749732734</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4848.436909087677</v>
+        <v>4848.375799001741</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -30652,46 +30652,46 @@
         <v>2760.937391194303</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.4849430367736</v>
+        <v>710.4849430367738</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>245.7140354696757</v>
+        <v>245.7140354696758</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>406.9924088095189</v>
+        <v>406.9921954129193</v>
       </c>
       <c r="N61" s="132" t="n">
-        <v>4124.128778510271</v>
+        <v>4124.128565113671</v>
       </c>
       <c r="P61" s="130" t="n">
         <v>2896.738881877362</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>758.54766362367</v>
+        <v>758.5476636236698</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>256.0029063005556</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>412.9240454842196</v>
+        <v>412.9234870249217</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>4324.213497285807</v>
+        <v>4324.212938826509</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>3030.200510783198</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>802.719726109169</v>
+        <v>802.7197261091691</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>266.1453571552707</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>427.7866374611582</v>
+        <v>427.7806947937877</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4526.852231508797</v>
+        <v>4526.846288841426</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -30702,10 +30702,10 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>764566.2716199862</v>
+        <v>764007.0967268042</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>2239.061706429667</v>
+        <v>2231.660200351779</v>
       </c>
     </row>
     <row r="62">
@@ -30805,55 +30805,55 @@
         <v>229</v>
       </c>
       <c r="G63" s="131" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H63" s="132" t="n">
-        <v>5063</v>
+        <v>5073</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>6063.963028375118</v>
+        <v>6063.95385411218</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1028.516213076215</v>
+        <v>1028.516213076213</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>482.4032427834436</v>
+        <v>477.505793182102</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>2644.761445481004</v>
+        <v>2653.723479434723</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10219.64392971578</v>
+        <v>10223.69933980522</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>6897.230573753623</v>
+        <v>6897.219061859658</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1192.650797495556</v>
+        <v>1192.650797495557</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>519.4264574542294</v>
+        <v>513.29853309591</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>2834.005975254689</v>
+        <v>2842.574994921451</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11443.3138039581</v>
+        <v>11445.74338737257</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>7858.821665971947</v>
+        <v>7858.807911385724</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1393.143371473848</v>
+        <v>1393.143371473847</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>544.4036228611685</v>
+        <v>537.0837375110368</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>3094.855133886602</v>
+        <v>3103.122540499337</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>12891.22379419357</v>
+        <v>12892.15756086994</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30886,10 +30886,10 @@
         <v>0</v>
       </c>
       <c r="G64" s="134" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H64" s="135" t="n">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="J64" s="133" t="n">
         <v>0</v>
@@ -30901,10 +30901,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>2262.80201387684</v>
+        <v>2271.76404783056</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>2406.657072991981</v>
+        <v>2415.226092658741</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -30931,10 +30931,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>2617.330548976011</v>
+        <v>2625.597955588746</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -31034,7 +31034,7 @@
         <v>347285.1570508346</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>905.9255220822611</v>
+        <v>905.9255220822612</v>
       </c>
     </row>
     <row r="66">
@@ -31144,16 +31144,16 @@
         <v>36007.66823156678</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>5431.185034624416</v>
+        <v>5431.185034624418</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>1643.87665807868</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>1362.310849873848</v>
+        <v>1362.310135579192</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>44445.04077414373</v>
+        <v>44445.04005984907</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>34052.38752490297</v>
@@ -31162,28 +31162,28 @@
         <v>4646.024039270555</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1463.882211566669</v>
+        <v>1463.88221156667</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>1412.269704923372</v>
+        <v>1412.267794898619</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41574.56348066356</v>
+        <v>41574.56157063881</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>33426.99961360797</v>
+        <v>33426.99961360798</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>4250.604456183502</v>
+        <v>4250.604456183503</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>1375.045066978046</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1620.213936787498</v>
+        <v>1620.19142932314</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>40672.86307355702</v>
+        <v>40672.84056609267</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -31216,55 +31216,55 @@
         <v>3358</v>
       </c>
       <c r="G68" s="143" t="n">
-        <v>6165</v>
+        <v>6175</v>
       </c>
       <c r="H68" s="144" t="n">
-        <v>48448</v>
+        <v>48468</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>48409.5719511969</v>
+        <v>48409.56277693396</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>8285.745345589618</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2999.721861871521</v>
+        <v>2994.82441227018</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>8039.03232728299</v>
+        <v>8047.991532881591</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>69996.87349981788</v>
+        <v>70009.88811550592</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>47464.74262830856</v>
+        <v>47464.73111641459</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>7740.263750551166</v>
+        <v>7740.263750551165</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2910.660891075922</v>
+        <v>2904.532966717603</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>8643.219611259963</v>
+        <v>8651.780774253313</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>69165.54395418758</v>
+        <v>69176.53470059541</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>47955.58247823487</v>
+        <v>47955.56872364866</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>7603.582751084724</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2906.407488326608</v>
+        <v>2899.087602976476</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>9541.903567953928</v>
+        <v>9550.081414348999</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>70624.80683457616</v>
+        <v>70633.91844764759</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31278,7 +31278,7 @@
         <v>187191.9019934708</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>346.6790497903377</v>
+        <v>346.6790497903376</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -31770,7 +31770,7 @@
         <v>128.2800174617996</v>
       </c>
       <c r="K76" s="131" t="n">
-        <v>42.93598052467679</v>
+        <v>42.9359805246768</v>
       </c>
       <c r="L76" s="131" t="n">
         <v>12.1098980688175</v>
@@ -31785,7 +31785,7 @@
         <v>131.7304208904419</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13363173601854</v>
+        <v>44.13363173601853</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44747003933478</v>
@@ -31794,13 +31794,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3115226657953</v>
+        <v>188.3115226657952</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.3980143349047</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.05511271165162</v>
+        <v>45.05511271165161</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70713982589314</v>
@@ -31843,10 +31843,10 @@
         <v>46.76876318724293</v>
       </c>
       <c r="M77" s="131" t="n">
-        <v>293.459219768103</v>
+        <v>293.454975391339</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>340.2279829553459</v>
+        <v>340.2237385785819</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -31858,10 +31858,10 @@
         <v>51.03944690346369</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>346.9012428180422</v>
+        <v>346.8954687025169</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>397.9406897215059</v>
+        <v>397.9349156059806</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -31870,13 +31870,13 @@
         <v>0</v>
       </c>
       <c r="X77" s="131" t="n">
-        <v>55.91397637446341</v>
+        <v>55.9139763744634</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>429.6897602068635</v>
+        <v>429.6820421563438</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>485.6037365813269</v>
+        <v>485.5960185308072</v>
       </c>
     </row>
     <row r="78">
@@ -31977,10 +31977,10 @@
         <v>51.20888766333687</v>
       </c>
       <c r="M79" s="131" t="n">
-        <v>6.696987462960856</v>
+        <v>6.696890602695233</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2866.74538671823</v>
+        <v>2866.745289857964</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>2967.764433241743</v>
@@ -31992,25 +31992,25 @@
         <v>62.88054748548265</v>
       </c>
       <c r="S79" s="131" t="n">
-        <v>7.015569293869917</v>
+        <v>7.015452520844691</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3178.989083907147</v>
+        <v>3178.988967134122</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3244.985982181512</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>170.896069546928</v>
+        <v>170.8960695469279</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>73.0050868260645</v>
+        <v>73.00508682606451</v>
       </c>
       <c r="Y79" s="131" t="n">
-        <v>7.392892254635247</v>
+        <v>7.392759464140354</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>3496.28003080914</v>
+        <v>3496.279898018644</v>
       </c>
     </row>
     <row r="80">
@@ -32111,10 +32111,10 @@
         <v>197.3705810333049</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>176.0290901661888</v>
+        <v>176.0265442118289</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1576.803216563795</v>
+        <v>1576.800670609435</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>1090.701571439859</v>
@@ -32126,10 +32126,10 @@
         <v>218.5733671538328</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>262.6291555824171</v>
+        <v>262.6247841622621</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>1743.814959403218</v>
+        <v>1743.810587983063</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>1148.288930966286</v>
@@ -32141,10 +32141,10 @@
         <v>257.0678553579128</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>346.9079872526063</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1930.5145187721</v>
+        <v>1930.508287640667</v>
       </c>
     </row>
     <row r="82">
@@ -32178,10 +32178,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>176.0290901661889</v>
+        <v>176.0265442118287</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -32193,10 +32193,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>262.629155582417</v>
+        <v>262.624784162262</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -32208,10 +32208,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>346.9079872526061</v>
+        <v>346.9017561211729</v>
       </c>
     </row>
     <row r="83">
@@ -32380,13 +32380,13 @@
         <v>251057.4170218568</v>
       </c>
       <c r="L85" s="140" t="n">
-        <v>57266.91038557481</v>
+        <v>57266.91038557482</v>
       </c>
       <c r="M85" s="140" t="n">
-        <v>969.9340240824498</v>
+        <v>969.9199956752398</v>
       </c>
       <c r="N85" s="141" t="n">
-        <v>1413346.604401443</v>
+        <v>1413346.590373036</v>
       </c>
       <c r="P85" s="139" t="n">
         <v>1115952.652029663</v>
@@ -32398,10 +32398,10 @@
         <v>57819.37211079447</v>
       </c>
       <c r="S85" s="140" t="n">
-        <v>1095.643510353989</v>
+        <v>1095.62527354356</v>
       </c>
       <c r="T85" s="141" t="n">
-        <v>1427459.890486034</v>
+        <v>1427459.872249224</v>
       </c>
       <c r="V85" s="139" t="n">
         <v>1125695.480763512</v>
@@ -32413,10 +32413,10 @@
         <v>58283.77647998057</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>1183.845442488683</v>
+        <v>1183.824178358655</v>
       </c>
       <c r="Z85" s="141" t="n">
-        <v>1438770.993451629</v>
+        <v>1438770.972187499</v>
       </c>
     </row>
     <row r="86" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -32450,10 +32450,10 @@
         <v>57574.36851552752</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>1446.119321479702</v>
+        <v>1446.098405881103</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>1418489.735973902</v>
+        <v>1418489.712512349</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>1120142.848455235</v>
@@ -32465,10 +32465,10 @@
         <v>58164.31294237659</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>1712.189478048319</v>
+        <v>1712.160978929183</v>
       </c>
       <c r="T86" s="144" t="n">
-        <v>1433231.575897314</v>
+        <v>1433231.543026775</v>
       </c>
       <c r="V86" s="142" t="n">
         <v>1130223.153690994</v>
@@ -32480,10 +32480,10 @@
         <v>58682.4705383649</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>1967.836082202788</v>
+        <v>1967.800736100312</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>1445222.459991917</v>
+        <v>1445222.418414683</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32993,7 +32993,7 @@
         <v>1187.174881897402</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>284.7110855447894</v>
+        <v>284.7110855447893</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -33005,16 +33005,16 @@
         <v>3773.958702206662</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>1202.170310029857</v>
+        <v>1202.170310029856</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>284.1315318890079</v>
+        <v>284.131531889008</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z94" s="132" t="n">
-        <v>5260.260544125527</v>
+        <v>5260.260544125526</v>
       </c>
     </row>
     <row r="95">
@@ -33045,13 +33045,13 @@
         <v>0</v>
       </c>
       <c r="L95" s="131" t="n">
-        <v>402.7734026265692</v>
+        <v>402.7734026265693</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>3918.426842886722</v>
+        <v>3918.420697846095</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4321.200245513292</v>
+        <v>4321.194100472664</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -33063,10 +33063,10 @@
         <v>450.1251471524772</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4330.921128415725</v>
+        <v>4330.909966110838</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>4781.046275568202</v>
+        <v>4781.035113263316</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -33075,13 +33075,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>505.3030256434705</v>
+        <v>505.3030256434706</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4828.737620025534</v>
+        <v>4828.668791889078</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5334.040645669004</v>
+        <v>5333.971817532548</v>
       </c>
     </row>
     <row r="96">
@@ -33173,49 +33173,49 @@
         <v>35788</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>5457.960764601422</v>
+        <v>5457.960764601421</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>822.3010812215867</v>
+        <v>822.3010812215869</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>296.9229231330126</v>
+        <v>296.9229231330127</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>413.6893962724798</v>
+        <v>413.6890860156146</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>6990.874165228502</v>
+        <v>6990.873854971635</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>5864.503315119106</v>
+        <v>5864.503315119105</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>899.8761975097219</v>
+        <v>899.8761975097217</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>318.8834537860382</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>419.9396147780895</v>
+        <v>419.9389395457664</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>7503.202581192956</v>
+        <v>7503.201905960631</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6275.186492964711</v>
+        <v>6275.18649296471</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>973.6157956560969</v>
+        <v>973.615795656097</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>339.1504439813352</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>435.1795297157934</v>
+        <v>435.173454257928</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8023.132262317936</v>
+        <v>8023.12618686007</v>
       </c>
     </row>
     <row r="98">
@@ -33301,55 +33301,55 @@
         <v>292</v>
       </c>
       <c r="G99" s="131" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H99" s="132" t="n">
-        <v>5915</v>
+        <v>5925</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>7101.643792012008</v>
+        <v>7101.634617748903</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>1194.238994803804</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>679.7738238167512</v>
+        <v>674.8763742154042</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>2820.790535647193</v>
+        <v>2829.750023646551</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11796.44714627976</v>
+        <v>11800.50001041466</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>7987.932145193219</v>
+        <v>7987.920633299276</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1364.561662722641</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>737.999824608065</v>
+        <v>731.8719002497455</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>3096.635130837106</v>
+        <v>3105.199779083713</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>13187.12876336103</v>
+        <v>13189.55397535537</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>9007.110596938059</v>
+        <v>9007.096842351835</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1571.393116669147</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>801.4714782190786</v>
+        <v>794.1515928689478</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>3441.763121139209</v>
+        <v>3450.02429662051</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14821.73831296549</v>
+        <v>14822.66584851044</v>
       </c>
     </row>
     <row r="100">
@@ -33368,10 +33368,10 @@
         <v>0</v>
       </c>
       <c r="G100" s="134" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="H100" s="135" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="J100" s="133" t="n">
         <v>0</v>
@@ -33383,10 +33383,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="134" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="N100" s="135" t="n">
-        <v>2438.831104043029</v>
+        <v>2447.790592042389</v>
       </c>
       <c r="P100" s="133" t="n">
         <v>0</v>
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>2669.286228574398</v>
+        <v>2677.850876821003</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33413,10 +33413,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>2964.238536228618</v>
+        <v>2972.499711709919</v>
       </c>
     </row>
     <row r="101">
@@ -33585,13 +33585,13 @@
         <v>256488.6020564813</v>
       </c>
       <c r="L103" s="140" t="n">
-        <v>58910.78704365349</v>
+        <v>58910.7870436535</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>2332.244873956298</v>
+        <v>2332.230131254431</v>
       </c>
       <c r="N103" s="141" t="n">
-        <v>1457791.645175586</v>
+        <v>1457791.630432884</v>
       </c>
       <c r="P103" s="139" t="n">
         <v>1150005.039554566</v>
@@ -33603,10 +33603,10 @@
         <v>59283.25432236114</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>2507.913215277361</v>
+        <v>2507.893068442178</v>
       </c>
       <c r="T103" s="141" t="n">
-        <v>1469034.453966697</v>
+        <v>1469034.433819862</v>
       </c>
       <c r="V103" s="139" t="n">
         <v>1159122.48037712</v>
@@ -33618,10 +33618,10 @@
         <v>59658.82154695861</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>2804.059379276181</v>
+        <v>2804.015607681795</v>
       </c>
       <c r="Z103" s="141" t="n">
-        <v>1479443.856525186</v>
+        <v>1479443.812753592</v>
       </c>
     </row>
     <row r="104" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -33640,55 +33640,55 @@
         <v>3504</v>
       </c>
       <c r="G104" s="143" t="n">
-        <v>7086</v>
+        <v>7096</v>
       </c>
       <c r="H104" s="144" t="n">
-        <v>52114</v>
+        <v>52134</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1156324.899075631</v>
+        <v>1156324.889901368</v>
       </c>
       <c r="K104" s="143" t="n">
         <v>259663.6372678835</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>60574.09037739904</v>
+        <v>60569.1929277977</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>9485.151648762692</v>
+        <v>9494.089938762692</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>1488486.609473719</v>
+        <v>1488499.600627854</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>1167607.591083543</v>
+        <v>1167607.579571649</v>
       </c>
       <c r="Q104" s="143" t="n">
         <v>260689.8596166228</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>61074.97383345251</v>
+        <v>61068.84590909419</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>10355.40908930828</v>
+        <v>10363.9417531825</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>1502397.119851501</v>
+        <v>1502408.07772737</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>1178178.736169229</v>
+        <v>1178178.722414643</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>261605.6744441866</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61588.87802669151</v>
+        <v>61581.55814134137</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>11509.73965015672</v>
+        <v>11517.88215044931</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>1515847.266826493</v>
+        <v>1515856.33686233</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -33710,7 +33710,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>1578675</v>
+        <v>1578685</v>
       </c>
     </row>
     <row r="109"/>
